--- a/data/trans_orig/IMC_inf_MED_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6783</t>
+          <t>7446</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17955</t>
+          <t>18529</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12525</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26410</t>
+          <t>25577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>21720</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40119</t>
+          <t>39491</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,09%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3907</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13100</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>5439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10844</t>
+          <t>11218</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24608</t>
+          <t>24936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,69%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17819</t>
+          <t>18612</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>32750</t>
+          <t>32933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>22764</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37211</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>36,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>45286</t>
+          <t>43873</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>66868</t>
+          <t>65665</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38505</t>
+          <t>38235</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55131</t>
+          <t>54789</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>30237</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>46327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>73025</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96635</t>
+          <t>97763</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>49,16%</t>
+          <t>49,74%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1376</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8881</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>11819</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>17013</t>
+          <t>16406</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6035</t>
+          <t>5584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15958</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30005</t>
+          <t>29086</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>23413</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41081</t>
+          <t>40465</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>12368</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24667</t>
+          <t>24947</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17191</t>
+          <t>18181</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>32001</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>32502</t>
+          <t>32297</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53151</t>
+          <t>51519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25696</t>
+          <t>25879</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41738</t>
+          <t>42242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>55484</t>
+          <t>54967</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,24%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>66541</t>
+          <t>66055</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>89032</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,92%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67019</t>
+          <t>67545</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85944</t>
+          <t>85521</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>59,62%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53352</t>
+          <t>53992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72686</t>
+          <t>73391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125187</t>
+          <t>124972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>153215</t>
+          <t>153021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>50,74%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3779</t>
+          <t>3701</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12304</t>
+          <t>11878</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1330</t>
+          <t>1351</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7511</t>
+          <t>7435</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6413</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11207</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>23041</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30458</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>31619</t>
+          <t>31812</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>48891</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8764</t>
+          <t>8773</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19572</t>
+          <t>19122</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19073</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34232</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,88%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14939</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27221</t>
+          <t>27628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14481</t>
+          <t>15261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27123</t>
+          <t>27809</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>33865</t>
+          <t>32617</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>52443</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65847</t>
+          <t>66506</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>43878</t>
+          <t>43799</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59950</t>
+          <t>60463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>38,04%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>97781</t>
+          <t>97833</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121450</t>
+          <t>121573</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,85%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3015</t>
+          <t>3009</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>10668</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3066</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11745</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19473</t>
+          <t>18775</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9922</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23556</t>
+          <t>23402</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14348</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>28410</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27931</t>
+          <t>26634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45980</t>
+          <t>46003</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10475</t>
+          <t>10364</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>23678</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11115</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>24483</t>
+          <t>23617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>23557</t>
+          <t>24428</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43303</t>
+          <t>43119</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28765</t>
+          <t>28518</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>46939</t>
+          <t>47398</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>29955</t>
+          <t>29433</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>47122</t>
+          <t>48228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>63632</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>88884</t>
+          <t>89803</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,36%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>66460</t>
+          <t>67035</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>87367</t>
+          <t>87705</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>61308</t>
+          <t>61717</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81513</t>
+          <t>82270</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132522</t>
+          <t>133940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>161381</t>
+          <t>162515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,95%</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,7 +3250,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>4735</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>712</t>
+          <t>715</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6166</t>
+          <t>6875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>43134</t>
+          <t>43209</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65908</t>
+          <t>66764</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69511</t>
+          <t>71559</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>99292</t>
+          <t>99828</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>121079</t>
+          <t>120901</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>158173</t>
+          <t>156064</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44112</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>66385</t>
+          <t>67086</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>51670</t>
+          <t>51423</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76430</t>
+          <t>77857</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>102188</t>
+          <t>101551</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>135198</t>
+          <t>135457</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>100942</t>
+          <t>101983</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>132154</t>
+          <t>132384</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>118765</t>
+          <t>119627</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>151172</t>
+          <t>151358</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>228336</t>
+          <t>228399</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>271120</t>
+          <t>274008</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,76%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>239245</t>
+          <t>238786</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>275693</t>
+          <t>273811</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>54,69%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>206413</t>
+          <t>206346</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>243271</t>
+          <t>243816</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>46,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>457611</t>
+          <t>452774</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>509599</t>
+          <t>506770</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>49,49%</t>
         </is>
       </c>
     </row>
@@ -3912,12 +3912,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>11757</t>
+          <t>11796</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>25641</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3927,12 +3927,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25439</t>
+          <t>25940</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>27334</t>
+          <t>26754</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2922</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10643</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7177</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18447</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12203</t>
+          <t>12037</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26473</t>
+          <t>25111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5585</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>15766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7904</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>31454</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27600</t>
+          <t>27924</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>31,74%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19240</t>
+          <t>18447</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>33199</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>36097</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>58366</t>
+          <t>56355</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39940</t>
+          <t>40152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55352</t>
+          <t>55780</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>35183</t>
+          <t>34548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52056</t>
+          <t>51527</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>52,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79378</t>
+          <t>79701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102467</t>
+          <t>102150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,17%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>757</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7007</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1509</t>
+          <t>2052</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8992</t>
+          <t>9466</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3836</t>
+          <t>3545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2857</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>7184</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18257</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12132</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24988</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13082</t>
+          <t>12845</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26883</t>
+          <t>26260</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>20431</t>
+          <t>20073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36162</t>
+          <t>36435</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19438</t>
+          <t>18927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33730</t>
+          <t>33465</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32465</t>
+          <t>32010</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49699</t>
+          <t>49741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>54432</t>
+          <t>55541</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>77879</t>
+          <t>78302</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,95%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>93453</t>
+          <t>93765</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110602</t>
+          <t>110262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>74,83%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65337</t>
+          <t>66832</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86157</t>
+          <t>88125</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>165445</t>
+          <t>164893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193313</t>
+          <t>191064</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>54,83%</t>
+          <t>54,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,32%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2297</t>
+          <t>1859</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>8865</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3475</t>
+          <t>3597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>7189</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>17855</t>
+          <t>17980</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4472</t>
+          <t>5062</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12858</t>
+          <t>13648</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>7154</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>17586</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>13314</t>
+          <t>13798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26607</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5310</t>
+          <t>5409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9290</t>
+          <t>9638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21971</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16953</t>
+          <t>16742</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31156</t>
+          <t>32265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14872</t>
+          <t>14745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27139</t>
+          <t>28400</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>10933</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22738</t>
+          <t>22703</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>29115</t>
+          <t>28788</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45920</t>
+          <t>45197</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,58%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57896</t>
+          <t>57111</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>73777</t>
+          <t>72702</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>51,94%</t>
+          <t>51,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56767</t>
+          <t>56783</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73794</t>
+          <t>74519</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>62,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>118152</t>
+          <t>119379</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>141517</t>
+          <t>142191</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>61,61%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4152</t>
+          <t>4584</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13047</t>
+          <t>13323</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7214</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18481</t>
+          <t>19325</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>12969</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>27436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5001</t>
+          <t>4522</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15866</t>
+          <t>14695</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20935</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16344</t>
+          <t>16904</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32086</t>
+          <t>32479</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,06%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>6771</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17849</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>10887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23897</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20512</t>
+          <t>20466</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>37936</t>
+          <t>38412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>26589</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>44927</t>
+          <t>44306</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>33080</t>
+          <t>33128</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53341</t>
+          <t>51593</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>33,88%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>64883</t>
+          <t>64691</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>90448</t>
+          <t>90381</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,77%</t>
         </is>
       </c>
     </row>
@@ -6759,12 +6759,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73037</t>
+          <t>71983</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>92097</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>60264</t>
+          <t>59610</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>81574</t>
+          <t>80198</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6809,12 +6809,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,57%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6829,12 +6829,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137291</t>
+          <t>138819</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>167300</t>
+          <t>168223</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6844,12 +6844,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,74%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>57,27%</t>
         </is>
       </c>
     </row>
@@ -6872,12 +6872,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6907,12 +6907,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4486</t>
+          <t>4344</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14870</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19720</t>
+          <t>18414</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>21614</t>
+          <t>21581</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>39029</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38951</t>
+          <t>40180</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>62316</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>64485</t>
+          <t>65191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>93991</t>
+          <t>93129</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>29645</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>49880</t>
+          <t>49464</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>52271</t>
+          <t>51503</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>76235</t>
+          <t>77241</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>87414</t>
+          <t>86894</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>118821</t>
+          <t>116293</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>87388</t>
+          <t>88337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>116286</t>
+          <t>118264</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>109532</t>
+          <t>108368</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141471</t>
+          <t>141606</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>204838</t>
+          <t>207218</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>248558</t>
+          <t>249326</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>282753</t>
+          <t>281515</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>315904</t>
+          <t>317666</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>236539</t>
+          <t>235991</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>273474</t>
+          <t>273740</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>527949</t>
+          <t>527304</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>580503</t>
+          <t>580139</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>52,2%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,36%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13288</t>
+          <t>13031</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>26973</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22712</t>
+          <t>23259</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>41507</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>40131</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>62936</t>
+          <t>62772</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,21%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC medido en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>993</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1552</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>7094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3672</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10764</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2415</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8359</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2747</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6356</t>
+          <t>6050</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16817</t>
+          <t>16060</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>16,72%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8967</t>
+          <t>9075</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25591</t>
+          <t>25517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16460</t>
+          <t>16225</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32185</t>
+          <t>31878</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -8355,12 +8355,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21405</t>
+          <t>21333</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30041</t>
+          <t>29815</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8370,12 +8370,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19056</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32423</t>
+          <t>32184</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8405,12 +8405,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8425,12 +8425,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43148</t>
+          <t>42716</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>60020</t>
+          <t>59355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,93%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>61,8%</t>
         </is>
       </c>
     </row>
@@ -8473,7 +8473,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8488,7 +8488,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7893</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1787</t>
+          <t>1874</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8957</t>
+          <t>9183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1347</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>7079</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18726</t>
+          <t>18841</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9771</t>
+          <t>10220</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22919</t>
+          <t>22870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6403</t>
+          <t>6651</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11065</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>25499</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13480</t>
+          <t>14523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29631</t>
+          <t>29656</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8115</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18867</t>
+          <t>18750</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>15988</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38073</t>
+          <t>36368</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>27282</t>
+          <t>27735</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>53570</t>
+          <t>53213</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36685</t>
+          <t>36909</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48853</t>
+          <t>49447</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9072,12 +9072,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39656</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59661</t>
+          <t>58489</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9087,12 +9087,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>79851</t>
+          <t>79577</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>105065</t>
+          <t>104087</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9122,12 +9122,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2481</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9582</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2591</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14665</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21926</t>
+          <t>22339</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -9385,7 +9385,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1510</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10967</t>
+          <t>9419</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>2033</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11841</t>
+          <t>11160</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>667</t>
+          <t>1071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10145</t>
+          <t>10536</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3113</t>
+          <t>3290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>12843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5552</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19143</t>
+          <t>18248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4436</t>
+          <t>4854</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27494</t>
+          <t>26788</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>32,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>9295</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>22266</t>
+          <t>23724</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15319</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>43428</t>
+          <t>41392</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -9719,12 +9719,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45149</t>
+          <t>44969</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>76283</t>
+          <t>75516</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9734,12 +9734,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40627</t>
+          <t>39952</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56762</t>
+          <t>56016</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>51,7%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93046</t>
+          <t>94207</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>131756</t>
+          <t>132210</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7817</t>
+          <t>8981</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>2909</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13822</t>
+          <t>12706</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>7,84%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14213</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1025</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3244</t>
+          <t>3160</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15444</t>
+          <t>16332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2446</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>10267</t>
+          <t>9844</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>16838</t>
+          <t>17002</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9025</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>23079</t>
+          <t>24290</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>7124</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18847</t>
+          <t>19057</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5298</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15646</t>
+          <t>15496</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14634</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29775</t>
+          <t>30092</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41728</t>
+          <t>41743</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>56241</t>
+          <t>56376</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>75,83%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10436,12 +10436,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38271</t>
+          <t>37714</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>52484</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10451,12 +10451,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>54,14%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>84418</t>
+          <t>85158</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>105209</t>
+          <t>106054</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,28%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>73,21%</t>
         </is>
       </c>
     </row>
@@ -10514,12 +10514,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>635</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6212</t>
+          <t>6206</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10529,12 +10529,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10549,12 +10549,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>675</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10564,12 +10564,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10584,12 +10584,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2384</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9669</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10599,12 +10599,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6363</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16619</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>31634</t>
+          <t>32357</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25380</t>
+          <t>26104</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>46834</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>11397</t>
+          <t>11191</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29386</t>
+          <t>30560</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>51839</t>
+          <t>51710</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>43780</t>
+          <t>44435</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>72849</t>
+          <t>72272</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,44%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>29689</t>
+          <t>30066</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>59920</t>
+          <t>58204</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>54543</t>
+          <t>52697</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>86087</t>
+          <t>85587</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>89454</t>
+          <t>89999</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>132714</t>
+          <t>132785</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>162262</t>
+          <t>161272</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>205337</t>
+          <t>202826</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11098,12 +11098,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>77,53%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>150833</t>
+          <t>152681</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>184544</t>
+          <t>185940</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,78%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>322935</t>
+          <t>323728</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>382799</t>
+          <t>384479</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>66,15%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>19503</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>10848</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>25924</t>
+          <t>26386</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>41172</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11281,7 +11281,7 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">

--- a/data/trans_orig/IMC_inf_MED_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IMC_inf_MED_R-Habitat-trans_orig.xlsx
@@ -545,7 +545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 70,03%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2012 (tasa de respuesta: 83,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -735,19 +735,19 @@
         <v>17956</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>12139</v>
+        <v>11837</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>26218</v>
+        <v>26322</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.1760495826121356</v>
+        <v>0.1415187463859629</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.1190154087867579</v>
+        <v>0.09329210391232683</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.257048248586581</v>
+        <v>0.2074527359847486</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>17</v>
@@ -756,19 +756,19 @@
         <v>12179</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>7558</v>
+        <v>7603</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>19776</v>
+        <v>18715</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.1287835884572573</v>
+        <v>0.1013381687718965</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.07992069206781865</v>
+        <v>0.06326352915239822</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.2091191751144643</v>
+        <v>0.1557273456969263</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>40</v>
@@ -777,19 +777,19 @@
         <v>30135</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>22576</v>
+        <v>21827</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>40785</v>
+        <v>39610</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.1533099381293182</v>
+        <v>0.1219737890750996</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.1148550138341484</v>
+        <v>0.08834691159430068</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.2074910611818404</v>
+        <v>0.1603253416747237</v>
       </c>
     </row>
     <row r="5">
@@ -800,67 +800,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>10116</v>
+        <v>15199</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>5816</v>
+        <v>10060</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>16614</v>
+        <v>22766</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.09918512304773795</v>
+        <v>0.1197868991299458</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.05702267331222789</v>
+        <v>0.07928152866608848</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1628894811281282</v>
+        <v>0.1794259953935315</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>7177</v>
+        <v>12391</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>3485</v>
+        <v>7605</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>12355</v>
+        <v>19545</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.07589115473170843</v>
+        <v>0.1031066595452152</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.03685458277060202</v>
+        <v>0.06327903124239724</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1306485001422357</v>
+        <v>0.162636598846545</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>17293</v>
+        <v>27590</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>11594</v>
+        <v>19640</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>24760</v>
+        <v>36803</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.08797840736193545</v>
+        <v>0.1116731638384849</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.05898570490759757</v>
+        <v>0.0794954499751741</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1259646640692463</v>
+        <v>0.1489623651561483</v>
       </c>
     </row>
     <row r="6">
@@ -871,67 +871,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>29477</v>
+        <v>35707</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>22152</v>
+        <v>27478</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>36765</v>
+        <v>44983</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.2890007837806932</v>
+        <v>0.2814135800837811</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.2171879475063056</v>
+        <v>0.2165610280902001</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.3604564069220214</v>
+        <v>0.3545205233437519</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>24911</v>
+        <v>30990</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>18220</v>
+        <v>22656</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>32554</v>
+        <v>39881</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.263427457263451</v>
+        <v>0.257871137150318</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1926739222620149</v>
+        <v>0.1885249062635242</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3442470063386401</v>
+        <v>0.3318519231580809</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>54388</v>
+        <v>66697</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>43833</v>
+        <v>55654</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>65297</v>
+        <v>79258</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2766974700846017</v>
+        <v>0.269961877060804</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.2229963877037545</v>
+        <v>0.2252644508322432</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3321963544907406</v>
+        <v>0.3208045083582722</v>
       </c>
     </row>
     <row r="7">
@@ -942,67 +942,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>37990</v>
+        <v>51565</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>30037</v>
+        <v>42639</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>46862</v>
+        <v>62111</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.3724657578366272</v>
+        <v>0.406397608418245</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.2944905656705081</v>
+        <v>0.336049531946312</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.459447230113237</v>
+        <v>0.4895083423741361</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>46633</v>
+        <v>60951</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>38533</v>
+        <v>51503</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>55168</v>
+        <v>70504</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.4931235509818378</v>
+        <v>0.5071730712007551</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4074768156415962</v>
+        <v>0.4285615364269214</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.5833795639249487</v>
+        <v>0.5866653846016791</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>84623</v>
+        <v>112516</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>72133</v>
+        <v>99638</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>95866</v>
+        <v>125186</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4305141575214614</v>
+        <v>0.4554176134810173</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.3669748476275723</v>
+        <v>0.4032932185917878</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.4877163089952831</v>
+        <v>0.5067023825222272</v>
       </c>
     </row>
     <row r="8">
@@ -1019,19 +1019,19 @@
         <v>6456</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>2819</v>
+        <v>3316</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>11485</v>
+        <v>12008</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.06329875272280615</v>
+        <v>0.05088316598206515</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.02763515219550694</v>
+        <v>0.02613644771181589</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1126042865600984</v>
+        <v>0.09463480942125409</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>5</v>
@@ -1040,19 +1040,19 @@
         <v>3667</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>1377</v>
+        <v>1383</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>7756</v>
+        <v>8031</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.0387742485657455</v>
+        <v>0.03051096333181538</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.01456095752144539</v>
+        <v>0.01150539694773524</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.08201335838177107</v>
+        <v>0.06682353537181465</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>14</v>
@@ -1061,19 +1061,19 @@
         <v>10123</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>5421</v>
+        <v>5710</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>16722</v>
+        <v>16066</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.05150002690268334</v>
+        <v>0.04097355654459416</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.02758082183839485</v>
+        <v>0.02311134067422177</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.08507380034587596</v>
+        <v>0.06502879169043287</v>
       </c>
     </row>
     <row r="9">
@@ -1084,16 +1084,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>140</v>
+        <v>173</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>101996</v>
+        <v>126884</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -1105,16 +1105,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>94566</v>
+        <v>120177</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -1126,16 +1126,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>269</v>
+        <v>335</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>196562</v>
+        <v>247061</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -1165,19 +1165,19 @@
         <v>21564</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>14648</v>
+        <v>15178</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>30017</v>
+        <v>29508</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1369830596780936</v>
+        <v>0.1132966063457963</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.09304637814091046</v>
+        <v>0.07974412510381283</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1906755512802753</v>
+        <v>0.1550308521653792</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>16</v>
@@ -1186,19 +1186,19 @@
         <v>9904</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>5661</v>
+        <v>5340</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>14860</v>
+        <v>15368</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.06870826790434752</v>
+        <v>0.05554630186093944</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.03927385080128507</v>
+        <v>0.02995092084690387</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1030910485889782</v>
+        <v>0.08619262005229061</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>46</v>
@@ -1207,19 +1207,19 @@
         <v>31468</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>22485</v>
+        <v>23562</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>40287</v>
+        <v>41231</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.1043487806839281</v>
+        <v>0.08536411223060927</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.07456029731427145</v>
+        <v>0.06391725815801082</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.133592756650229</v>
+        <v>0.1118461304579593</v>
       </c>
     </row>
     <row r="11">
@@ -1230,67 +1230,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>24201</v>
+        <v>30843</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>16788</v>
+        <v>23453</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>31588</v>
+        <v>40302</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1537307997582074</v>
+        <v>0.1620469750966513</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.106643745359965</v>
+        <v>0.1232219949026811</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.2006548547771794</v>
+        <v>0.2117414805045631</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>17943</v>
+        <v>21131</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>12577</v>
+        <v>14949</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>25461</v>
+        <v>28517</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.1244809242449077</v>
+        <v>0.1185103231072303</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.08725516456649025</v>
+        <v>0.08384011027461348</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.1766358041755555</v>
+        <v>0.1599393316787684</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>63</v>
+        <v>77</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>42144</v>
+        <v>51974</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>33047</v>
+        <v>41320</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>53431</v>
+        <v>63255</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1397498182971598</v>
+        <v>0.1409892978023554</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.1095835927563976</v>
+        <v>0.1120882307984468</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1771767282112582</v>
+        <v>0.1715920857393561</v>
       </c>
     </row>
     <row r="12">
@@ -1301,67 +1301,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
+        <v>75</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>51108</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>42166</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>61418</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.2685171362036019</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2215360688238488</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.3226815784967424</v>
+      </c>
+      <c r="J12" s="5" t="n">
         <v>67</v>
       </c>
-      <c r="D12" s="5" t="n">
-        <v>45320</v>
-      </c>
-      <c r="E12" s="5" t="n">
-        <v>36197</v>
-      </c>
-      <c r="F12" s="5" t="n">
-        <v>54550</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>0.2878852531852968</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>0.2299323980519448</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>0.346519860950859</v>
-      </c>
-      <c r="J12" s="5" t="n">
-        <v>49</v>
-      </c>
       <c r="K12" s="5" t="n">
-        <v>32790</v>
+        <v>43986</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>25619</v>
+        <v>35548</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>41294</v>
+        <v>53558</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2274779791549796</v>
+        <v>0.2466968855173517</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.1777324582811791</v>
+        <v>0.1993681132864572</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2864782018520093</v>
+        <v>0.3003796635489142</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>78110</v>
+        <v>95095</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>66431</v>
+        <v>81237</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>90569</v>
+        <v>109429</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2590115242032272</v>
+        <v>0.2579631827773406</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.2202862277166845</v>
+        <v>0.2203728302115278</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.3003283332896823</v>
+        <v>0.2968490561150958</v>
       </c>
     </row>
     <row r="13">
@@ -1372,67 +1372,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>62953</v>
+        <v>83435</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>53090</v>
+        <v>71986</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>72770</v>
+        <v>94996</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3998998490912227</v>
+        <v>0.4383561004293171</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3372450432910598</v>
+        <v>0.3782078462204317</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.4622565605037176</v>
+        <v>0.4991010018874337</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>76390</v>
+        <v>96162</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>66011</v>
+        <v>85905</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>85717</v>
+        <v>107609</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.5299517513949183</v>
+        <v>0.5393250024848563</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.4579485912097994</v>
+        <v>0.4817964481385789</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.5946573130596794</v>
+        <v>0.6035224309641603</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>208</v>
+        <v>270</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>139343</v>
+        <v>179597</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>126653</v>
+        <v>164432</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>154021</v>
+        <v>194666</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.462062617416688</v>
+        <v>0.4871924362311963</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4199806547631084</v>
+        <v>0.4460542415560137</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5107335127282854</v>
+        <v>0.5280721325034945</v>
       </c>
     </row>
     <row r="14">
@@ -1449,19 +1449,19 @@
         <v>3385</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1336</v>
+        <v>693</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>7518</v>
+        <v>7434</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.02150103828717943</v>
+        <v>0.01778318192463347</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.008485885411213014</v>
+        <v>0.003641499967504356</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.04775492006341993</v>
+        <v>0.03905716607622116</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>11</v>
@@ -1470,19 +1470,19 @@
         <v>7118</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>3787</v>
+        <v>3839</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>12382</v>
+        <v>12823</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.04938107730084684</v>
+        <v>0.03992148702962229</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.02627448387867068</v>
+        <v>0.02153343076233269</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.08589950190465628</v>
+        <v>0.07191503634468979</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>16</v>
@@ -1491,19 +1491,19 @@
         <v>10503</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>5935</v>
+        <v>6569</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>16310</v>
+        <v>16352</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.03482725939899697</v>
+        <v>0.02849097095849846</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.01968022129695619</v>
+        <v>0.01781970149649756</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.05408248952755607</v>
+        <v>0.04435852590077102</v>
       </c>
     </row>
     <row r="15">
@@ -1514,16 +1514,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>229</v>
+        <v>277</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>157423</v>
+        <v>190335</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -1535,16 +1535,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>220</v>
+        <v>274</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>144145</v>
+        <v>178301</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -1556,16 +1556,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>449</v>
+        <v>551</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>301568</v>
+        <v>368636</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -1595,19 +1595,19 @@
         <v>23622</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>16940</v>
+        <v>16921</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>31210</v>
+        <v>30898</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.204784178269019</v>
+        <v>0.1719248538265991</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.1468608742348015</v>
+        <v>0.1231580015174217</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.2705666468645582</v>
+        <v>0.2248854825293981</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>26</v>
@@ -1616,19 +1616,19 @@
         <v>16444</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>11513</v>
+        <v>11134</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>23798</v>
+        <v>23100</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.1434026498112603</v>
+        <v>0.126202510481623</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.1004002283031182</v>
+        <v>0.08545078872543822</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.2075346362939704</v>
+        <v>0.1772820336448458</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>62</v>
@@ -1637,19 +1637,19 @@
         <v>40066</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>31101</v>
+        <v>31528</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>49371</v>
+        <v>49482</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.1741839358732933</v>
+        <v>0.1496696991563357</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.1352105909788816</v>
+        <v>0.117775245019861</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.2146400394240212</v>
+        <v>0.1848463451325454</v>
       </c>
     </row>
     <row r="17">
@@ -1660,67 +1660,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>12647</v>
+        <v>13301</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>7868</v>
+        <v>8564</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>18760</v>
+        <v>20159</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.1096392945847098</v>
+        <v>0.09680532900267629</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.06821131127993933</v>
+        <v>0.06233342536072208</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.162639401941107</v>
+        <v>0.1467205925868371</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>13484</v>
+        <v>17463</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>8418</v>
+        <v>12041</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>19832</v>
+        <v>24288</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.1175912868261443</v>
+        <v>0.134025927900831</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.07340837221569395</v>
+        <v>0.09240694640771727</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1729492466721206</v>
+        <v>0.1864041162705902</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>26131</v>
+        <v>30764</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>19421</v>
+        <v>23108</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>34263</v>
+        <v>40108</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.113603563579482</v>
+        <v>0.1149222959994977</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.0844316768403906</v>
+        <v>0.08632124454777952</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.148956807989797</v>
+        <v>0.1498259213092968</v>
       </c>
     </row>
     <row r="18">
@@ -1731,67 +1731,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>20863</v>
+        <v>31050</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>14617</v>
+        <v>23600</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>27680</v>
+        <v>38465</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.1808655047978083</v>
+        <v>0.2259932559913796</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1267198681690615</v>
+        <v>0.1717703281656948</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.2399703674275535</v>
+        <v>0.2799584238456633</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>20943</v>
+        <v>25036</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>15503</v>
+        <v>17820</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>28766</v>
+        <v>32139</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1826382034610078</v>
+        <v>0.1921394918441433</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1351973537636342</v>
+        <v>0.1367605660571642</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2508621072749435</v>
+        <v>0.2466519411486771</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>41806</v>
+        <v>56086</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>32809</v>
+        <v>46404</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>51322</v>
+        <v>67845</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.1817492398586877</v>
+        <v>0.2095150813802757</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1426353718265416</v>
+        <v>0.1733468634244638</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.2231224826260707</v>
+        <v>0.2534439710648748</v>
       </c>
     </row>
     <row r="19">
@@ -1802,67 +1802,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>51871</v>
+        <v>63076</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>43815</v>
+        <v>54784</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>60863</v>
+        <v>72198</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.4496898043699405</v>
+        <v>0.4590839551964149</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.379843762560332</v>
+        <v>0.3987340517095566</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.5276424597855005</v>
+        <v>0.5254782279756431</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>57767</v>
+        <v>65324</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>48830</v>
+        <v>56577</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>65957</v>
+        <v>74171</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5037683365042339</v>
+        <v>0.5013414892881761</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.4258329997923559</v>
+        <v>0.4342121026109655</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.5751913502282647</v>
+        <v>0.5692334431615631</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>171</v>
+        <v>199</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>109638</v>
+        <v>128400</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>99018</v>
+        <v>116336</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>122017</v>
+        <v>141547</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.4766493186292379</v>
+        <v>0.4796526288118588</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.4304778501930238</v>
+        <v>0.4345852144195821</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.5304632934653013</v>
+        <v>0.5287637853167106</v>
       </c>
     </row>
     <row r="20">
@@ -1879,19 +1879,19 @@
         <v>6347</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>2850</v>
+        <v>3045</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>11423</v>
+        <v>12031</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.05502121797852245</v>
+        <v>0.04619260598293014</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.02470798786376001</v>
+        <v>0.02216291715946625</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.09903400237100449</v>
+        <v>0.0875629896803622</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>10</v>
@@ -1900,19 +1900,19 @@
         <v>6032</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>2922</v>
+        <v>3142</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>10909</v>
+        <v>10494</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.05259952339735374</v>
+        <v>0.0462905804852266</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.0254805606322143</v>
+        <v>0.02411015521825153</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.09513141860957648</v>
+        <v>0.08053441901349513</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>19</v>
@@ -1921,19 +1921,19 @@
         <v>12378</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>7474</v>
+        <v>7527</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>19754</v>
+        <v>18527</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.05381394205929906</v>
+        <v>0.04624029465203221</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.03249286617047227</v>
+        <v>0.02811805060522142</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.08588097938578503</v>
+        <v>0.06920941891359153</v>
       </c>
     </row>
     <row r="21">
@@ -1944,16 +1944,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>180</v>
+        <v>214</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>115349</v>
+        <v>137395</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -1965,16 +1965,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>114670</v>
+        <v>130299</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -1986,16 +1986,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>230019</v>
+        <v>267694</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -2025,19 +2025,19 @@
         <v>20431</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>14134</v>
+        <v>13783</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>28156</v>
+        <v>29110</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.1376158565570053</v>
+        <v>0.1193047076504264</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.09520302445648984</v>
+        <v>0.08048165188732541</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1896463474067445</v>
+        <v>0.1699805133690428</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>21</v>
@@ -2046,19 +2046,19 @@
         <v>15779</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>10357</v>
+        <v>10493</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>23465</v>
+        <v>23795</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.1071323913274666</v>
+        <v>0.09425544500736467</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.07031792087587999</v>
+        <v>0.06267751345376359</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1593159213251017</v>
+        <v>0.1421348753968253</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>48</v>
@@ -2067,19 +2067,19 @@
         <v>36211</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>26125</v>
+        <v>27377</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>45957</v>
+        <v>47894</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.1224347685779723</v>
+        <v>0.1069221392726613</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.08833428947219281</v>
+        <v>0.08083861428442357</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1553902557707222</v>
+        <v>0.141420728955521</v>
       </c>
     </row>
     <row r="23">
@@ -2090,67 +2090,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>16342</v>
+        <v>18867</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10943</v>
+        <v>12676</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>23383</v>
+        <v>26555</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1100728117821848</v>
+        <v>0.1101689275300662</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.07370432594295213</v>
+        <v>0.0740170997733713</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1574993585490003</v>
+        <v>0.1550619770115452</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>16297</v>
+        <v>20045</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>10377</v>
+        <v>13292</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>23689</v>
+        <v>28117</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.110645054362867</v>
+        <v>0.1197356251984291</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.07045508030764845</v>
+        <v>0.07939612941597399</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1608352411033996</v>
+        <v>0.1679536382963297</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>32639</v>
+        <v>38912</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>23978</v>
+        <v>29634</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>43292</v>
+        <v>49951</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.1103577946375548</v>
+        <v>0.1148980203467253</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.08107503764885574</v>
+        <v>0.08750167248072785</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1463783433580546</v>
+        <v>0.1474937137526119</v>
       </c>
     </row>
     <row r="24">
@@ -2161,67 +2161,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>38377</v>
+        <v>45431</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>29673</v>
+        <v>36384</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>47643</v>
+        <v>55269</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2584922435779479</v>
+        <v>0.2652871378318211</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.1998643524099806</v>
+        <v>0.2124590630506071</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.3209029748169326</v>
+        <v>0.3227375684540292</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>37663</v>
+        <v>41803</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>28069</v>
+        <v>33406</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>47396</v>
+        <v>53602</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2557078279173282</v>
+        <v>0.2497052106859783</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.1905719254921537</v>
+        <v>0.1995458999872891</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3217898104115202</v>
+        <v>0.3201843394895391</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>76040</v>
+        <v>87234</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>62476</v>
+        <v>73910</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>89773</v>
+        <v>101045</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2571055751399678</v>
+        <v>0.2575845447020311</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.2112439528693116</v>
+        <v>0.218240173211638</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.3035383953958186</v>
+        <v>0.2983630929471692</v>
       </c>
     </row>
     <row r="25">
@@ -2232,67 +2232,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>71774</v>
+        <v>84982</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>61846</v>
+        <v>74370</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>81505</v>
+        <v>96775</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.4834393192388589</v>
+        <v>0.4962405889063266</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.41656767914879</v>
+        <v>0.434269949173042</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5489777400433683</v>
+        <v>0.5651035933002421</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>100</v>
+        <v>116</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>76816</v>
+        <v>89049</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>66134</v>
+        <v>77130</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>87268</v>
+        <v>99210</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.5215314438857013</v>
+        <v>0.5319194100823539</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.4490072390474998</v>
+        <v>0.4607212755570386</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.592497053059112</v>
+        <v>0.5926126898479888</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>198</v>
+        <v>232</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>148590</v>
+        <v>174031</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>133704</v>
+        <v>157574</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>162884</v>
+        <v>190507</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5024096000523292</v>
+        <v>0.5138776526852312</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4520775684130091</v>
+        <v>0.4652824331559737</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5507426251619508</v>
+        <v>0.5625262504445526</v>
       </c>
     </row>
     <row r="26">
@@ -2312,16 +2312,16 @@
         <v>0</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>5090</v>
+        <v>4760</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.01037976884400312</v>
+        <v>0.008998638081359662</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.03428249694074072</v>
+        <v>0.02779715572532142</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>1</v>
@@ -2333,16 +2333,16 @@
         <v>0</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>4803</v>
+        <v>3644</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.004983282506636971</v>
+        <v>0.004384309025874057</v>
       </c>
       <c r="O26" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.03260954517806261</v>
+        <v>0.02176922588434817</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>3</v>
@@ -2351,19 +2351,19 @@
         <v>2275</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>6189</v>
+        <v>6057</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.007692261592176002</v>
+        <v>0.006717642993351154</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.002427879864921688</v>
+        <v>0.002107598727822186</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.02092554208366379</v>
+        <v>0.01788456482482955</v>
       </c>
     </row>
     <row r="27">
@@ -2374,16 +2374,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>203</v>
+        <v>232</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>148466</v>
+        <v>171252</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -2395,16 +2395,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>147289</v>
+        <v>167411</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -2416,16 +2416,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>394</v>
+        <v>448</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>295754</v>
+        <v>338663</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -2455,19 +2455,19 @@
         <v>83574</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>70758</v>
+        <v>71225</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>99010</v>
+        <v>99227</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.1597250072999284</v>
+        <v>0.1335326383457107</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.1352310964520681</v>
+        <v>0.1138016460046284</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1892277508849157</v>
+        <v>0.158543575909549</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>80</v>
@@ -2476,19 +2476,19 @@
         <v>54306</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>44362</v>
+        <v>43336</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>67459</v>
+        <v>65959</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.1084664916291259</v>
+        <v>0.09108860998299645</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.08860513025758981</v>
+        <v>0.07268877310993178</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.1347370218607096</v>
+        <v>0.1106342565805754</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>196</v>
@@ -2497,19 +2497,19 @@
         <v>137879</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>120549</v>
+        <v>120328</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>157141</v>
+        <v>157805</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.1346605456582088</v>
+        <v>0.1128260123870841</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.1177350154829054</v>
+        <v>0.09846397032856438</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.1534719792042908</v>
+        <v>0.1291311835642532</v>
       </c>
     </row>
     <row r="29">
@@ -2520,67 +2520,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>63306</v>
+        <v>78209</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>50655</v>
+        <v>65450</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>76045</v>
+        <v>93184</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1209900700982077</v>
+        <v>0.1249620234729365</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09681205943232604</v>
+        <v>0.1045750566185443</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1453359427475905</v>
+        <v>0.1488887874087832</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>54901</v>
+        <v>71030</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>43747</v>
+        <v>58829</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>66882</v>
+        <v>86348</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.1096550973152521</v>
+        <v>0.1191403589241443</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.08737726512906233</v>
+        <v>0.09867476264798246</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1335852034172904</v>
+        <v>0.1448337675106713</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>170</v>
+        <v>210</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>118207</v>
+        <v>149240</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>101934</v>
+        <v>129995</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>135501</v>
+        <v>168877</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1154474790416712</v>
+        <v>0.1221218823525349</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.09955378330818683</v>
+        <v>0.1063739806341852</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1323380834695329</v>
+        <v>0.13819126841729</v>
       </c>
     </row>
     <row r="30">
@@ -2591,67 +2591,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>195</v>
+        <v>235</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>134037</v>
+        <v>163296</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>118593</v>
+        <v>146696</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>150566</v>
+        <v>182431</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2561696973185351</v>
+        <v>0.2609127000597699</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.226652974890583</v>
+        <v>0.2343887875967914</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2877598635714188</v>
+        <v>0.2914862564145228</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>116307</v>
+        <v>141815</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>102241</v>
+        <v>126567</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>132417</v>
+        <v>160317</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2323030171496264</v>
+        <v>0.237870412302293</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.2042080616132547</v>
+        <v>0.2122944254963693</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2644795750005397</v>
+        <v>0.2689039442236753</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>359</v>
+        <v>437</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>250344</v>
+        <v>305112</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>228000</v>
+        <v>280777</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>274451</v>
+        <v>329367</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.244499334223149</v>
+        <v>0.249671353462135</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.2226775305922569</v>
+        <v>0.2297584387082437</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2680433185906281</v>
+        <v>0.2695192623160355</v>
       </c>
     </row>
     <row r="31">
@@ -2662,67 +2662,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>324</v>
+        <v>409</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>224589</v>
+        <v>283058</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>205397</v>
+        <v>262180</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>242386</v>
+        <v>303916</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4292323533280058</v>
+        <v>0.4522660199957924</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.3925537144296473</v>
+        <v>0.4189075394729864</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.4632455520061621</v>
+        <v>0.4855930397726698</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>369</v>
+        <v>446</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>257606</v>
+        <v>311486</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>240625</v>
+        <v>290995</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>276260</v>
+        <v>331750</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.5145216830855965</v>
+        <v>0.5224630132644862</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.480606662493651</v>
+        <v>0.4880927559959314</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.5517803847176144</v>
+        <v>0.5564513623275738</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>693</v>
+        <v>855</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>482195</v>
+        <v>594544</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>456249</v>
+        <v>566064</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>507772</v>
+        <v>622981</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.4709372506739659</v>
+        <v>0.486512130440671</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.4455972751771586</v>
+        <v>0.4632068362608711</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.4959176594829832</v>
+        <v>0.5097815840109283</v>
       </c>
     </row>
     <row r="32">
@@ -2739,19 +2739,19 @@
         <v>17729</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>11540</v>
+        <v>11734</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>26157</v>
+        <v>25977</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.03388287195532295</v>
+        <v>0.02832661812579045</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.02205505524700879</v>
+        <v>0.01874903936099447</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.04999061100541763</v>
+        <v>0.04150608855043674</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>27</v>
@@ -2760,19 +2760,19 @@
         <v>17550</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>11218</v>
+        <v>11728</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>24693</v>
+        <v>24750</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.0350537108203991</v>
+        <v>0.02943760552608009</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02240678910564161</v>
+        <v>0.01967173660685467</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.04931933223154731</v>
+        <v>0.04151435620132864</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>52</v>
@@ -2781,19 +2781,19 @@
         <v>35279</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>26343</v>
+        <v>26212</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>45413</v>
+        <v>46083</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.03445539040300503</v>
+        <v>0.02886862135757496</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.02572817312631482</v>
+        <v>0.02144903448420012</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.04435299021328579</v>
+        <v>0.03770962350672428</v>
       </c>
     </row>
     <row r="33">
@@ -2804,16 +2804,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>752</v>
+        <v>896</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>523234</v>
+        <v>625866</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -2825,16 +2825,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>718</v>
+        <v>854</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>500670</v>
+        <v>596188</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -2846,16 +2846,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1470</v>
+        <v>1750</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>1023904</v>
+        <v>1222054</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -2927,7 +2927,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 69,19%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2016 (tasa de respuesta: 82,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3117,19 +3117,19 @@
         <v>11976</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>7024</v>
+        <v>7449</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>18161</v>
+        <v>18759</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.121979850844778</v>
+        <v>0.09861380942594511</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.07154296026023398</v>
+        <v>0.06133686562378891</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1849741888602377</v>
+        <v>0.1544619031606706</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>9</v>
@@ -3138,19 +3138,19 @@
         <v>6084</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>2989</v>
+        <v>3120</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>10978</v>
+        <v>11295</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.06995269497040606</v>
+        <v>0.05649334061337901</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.03437487199322677</v>
+        <v>0.02897025304054769</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1262370441784719</v>
+        <v>0.1048893278562875</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>25</v>
@@ -3159,19 +3159,19 @@
         <v>18060</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>12105</v>
+        <v>11818</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>25785</v>
+        <v>25342</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.09754186937983865</v>
+        <v>0.07881811993663967</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.06537904077741437</v>
+        <v>0.0515770711360431</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1392675125842534</v>
+        <v>0.1106006941914388</v>
       </c>
     </row>
     <row r="5">
@@ -3182,67 +3182,67 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>12946</v>
+        <v>18244</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>8183</v>
+        <v>11834</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>19363</v>
+        <v>26809</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1318550364094862</v>
+        <v>0.1502230357507938</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.08334312977190568</v>
+        <v>0.09744251464513405</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1972141666552261</v>
+        <v>0.2207503258700399</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>9724</v>
+        <v>10352</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>5636</v>
+        <v>5891</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>15429</v>
+        <v>15982</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1118152328244749</v>
+        <v>0.09613214244355188</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.06480399702684382</v>
+        <v>0.05470850624169883</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1774130393829381</v>
+        <v>0.1484113907002769</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>22670</v>
+        <v>28596</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>15906</v>
+        <v>21046</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>31092</v>
+        <v>38153</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1224420223720849</v>
+        <v>0.1248015112925983</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.08590740067594468</v>
+        <v>0.09184896259315127</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1679300045434011</v>
+        <v>0.1665111424461401</v>
       </c>
     </row>
     <row r="6">
@@ -3253,67 +3253,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>30824</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>22595</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>39596</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.2538121350158197</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.1860523612328818</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.3260394852553173</v>
+      </c>
+      <c r="J6" s="5" t="n">
         <v>34</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>25667</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>19091</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>34488</v>
-      </c>
-      <c r="G6" s="6" t="n">
-        <v>0.261427274858855</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>0.1944512034467284</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>0.351271534892972</v>
-      </c>
-      <c r="J6" s="5" t="n">
-        <v>28</v>
-      </c>
       <c r="K6" s="5" t="n">
-        <v>20517</v>
+        <v>25070</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>14628</v>
+        <v>18073</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>28875</v>
+        <v>33444</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.2359118326867895</v>
+        <v>0.2328068094653848</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.1682001864817507</v>
+        <v>0.1678316939323699</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.3320222424327192</v>
+        <v>0.3105685448879161</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>46184</v>
+        <v>55894</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>36255</v>
+        <v>44458</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>57437</v>
+        <v>66849</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.2494422664071856</v>
+        <v>0.2439400962199426</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1958136380162302</v>
+        <v>0.1940269199899038</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3102237493626809</v>
+        <v>0.2917486910734581</v>
       </c>
     </row>
     <row r="7">
@@ -3324,67 +3324,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>43253</v>
+        <v>56062</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>35192</v>
+        <v>46239</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>52327</v>
+        <v>65486</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4405453063020761</v>
+        <v>0.461623857841162</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3584364235085364</v>
+        <v>0.3807381924658856</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5329665411308366</v>
+        <v>0.5392227565781559</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>47835</v>
+        <v>63374</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>39808</v>
+        <v>54107</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>54871</v>
+        <v>71110</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.5500414124666921</v>
+        <v>0.5884995370948282</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.4577386056404906</v>
+        <v>0.502445286945319</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.6309392352672173</v>
+        <v>0.6603429629706213</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>125</v>
+        <v>162</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>91089</v>
+        <v>119436</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>80162</v>
+        <v>106338</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>103003</v>
+        <v>133080</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.4919773665014694</v>
+        <v>0.5212526231672732</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4329631423884154</v>
+        <v>0.4640914965380438</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.5563252855617091</v>
+        <v>0.5808020620123009</v>
       </c>
     </row>
     <row r="8">
@@ -3401,19 +3401,19 @@
         <v>4339</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1503</v>
+        <v>1588</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>9024</v>
+        <v>8768</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.04419253158480466</v>
+        <v>0.03572716196627941</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.01531328754521857</v>
+        <v>0.01307546517256273</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.09191693850765799</v>
+        <v>0.07219652482902535</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>4</v>
@@ -3422,19 +3422,19 @@
         <v>2807</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>751</v>
+        <v>724</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>7013</v>
+        <v>6777</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.03227882705163748</v>
+        <v>0.02606817038285614</v>
       </c>
       <c r="O8" s="6" t="n">
-        <v>0.00863499240812448</v>
+        <v>0.006719494921341811</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.08064424682345042</v>
+        <v>0.06293449115411567</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>10</v>
@@ -3443,19 +3443,19 @@
         <v>7146</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>3653</v>
+        <v>3600</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>12989</v>
+        <v>12999</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.03859647533942148</v>
+        <v>0.03118764938354629</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01973277529718429</v>
+        <v>0.01571078477633677</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.07015662294669685</v>
+        <v>0.05673182210234719</v>
       </c>
     </row>
     <row r="9">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>98181</v>
+        <v>121445</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -3487,16 +3487,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>86967</v>
+        <v>107687</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -3508,16 +3508,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>185148</v>
+        <v>229132</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -3547,19 +3547,19 @@
         <v>11860</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>7124</v>
+        <v>7203</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17738</v>
+        <v>17550</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.07681251952571508</v>
+        <v>0.06488216545997805</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.04614018000220019</v>
+        <v>0.03940565510091135</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1148851697663935</v>
+        <v>0.09601023546373944</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>10</v>
@@ -3568,19 +3568,19 @@
         <v>5693</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>2847</v>
+        <v>2856</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>9759</v>
+        <v>9694</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.03863597894579548</v>
+        <v>0.03331626079751814</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.01931951449491667</v>
+        <v>0.01671367442753236</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.06622902003704934</v>
+        <v>0.05673145846442985</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>28</v>
@@ -3589,19 +3589,19 @@
         <v>17553</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>12207</v>
+        <v>11922</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>25646</v>
+        <v>25583</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.05817035876328372</v>
+        <v>0.04963095067900511</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.04045568868865225</v>
+        <v>0.03371006322430953</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.0849902582797108</v>
+        <v>0.07233608423112282</v>
       </c>
     </row>
     <row r="11">
@@ -3612,67 +3612,67 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>18678</v>
+        <v>22771</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>12913</v>
+        <v>16005</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>26624</v>
+        <v>30731</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1209692973371664</v>
+        <v>0.1245713620370127</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.08363525310712577</v>
+        <v>0.08755843105565372</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.1724338563788335</v>
+        <v>0.1681197882438323</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>8485</v>
+        <v>9058</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>4864</v>
+        <v>5129</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>13789</v>
+        <v>13971</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.05758711878892621</v>
+        <v>0.05300888379698666</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.03300957431250733</v>
+        <v>0.03001646417507442</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.09357813718856114</v>
+        <v>0.08176017822458442</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>27163</v>
+        <v>31828</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>19534</v>
+        <v>23365</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>35517</v>
+        <v>42124</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.09001885646377518</v>
+        <v>0.08999561527581453</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.06473491775251301</v>
+        <v>0.0660663029370513</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1177043145495689</v>
+        <v>0.1191069093065667</v>
       </c>
     </row>
     <row r="12">
@@ -3683,67 +3683,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>40737</v>
+        <v>47791</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>32702</v>
+        <v>38955</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>50985</v>
+        <v>58137</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2638377853741914</v>
+        <v>0.261452703006851</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.2117992752615013</v>
+        <v>0.2131101405474214</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.3302112846142111</v>
+        <v>0.3180525356424676</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>25783</v>
+        <v>30499</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>19207</v>
+        <v>22418</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>33090</v>
+        <v>38807</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1749836044117114</v>
+        <v>0.1784846787468881</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.130351949048183</v>
+        <v>0.1311942886358969</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2245708178842549</v>
+        <v>0.227108681277782</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>66520</v>
+        <v>78290</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>55143</v>
+        <v>66734</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>78344</v>
+        <v>90459</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2204489947516072</v>
+        <v>0.2213663132305265</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1827455406163287</v>
+        <v>0.1886903047219496</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2596325918557489</v>
+        <v>0.2557747514393674</v>
       </c>
     </row>
     <row r="13">
@@ -3754,67 +3754,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>76157</v>
+        <v>93400</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>66146</v>
+        <v>81597</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>85490</v>
+        <v>103837</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4932429345585824</v>
+        <v>0.5109669592554457</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.4284078854477986</v>
+        <v>0.4463942612190199</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.553688751639112</v>
+        <v>0.5680632468654442</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>161</v>
+        <v>191</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>102634</v>
+        <v>120874</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>94027</v>
+        <v>111606</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>110877</v>
+        <v>130215</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6965421023636547</v>
+        <v>0.7073795900165263</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.6381307045986101</v>
+        <v>0.6531397075957369</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7524815878219787</v>
+        <v>0.762042903375069</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>273</v>
+        <v>328</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>178791</v>
+        <v>214274</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>165937</v>
+        <v>199492</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>193131</v>
+        <v>230057</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5925168790155646</v>
+        <v>0.60586464235577</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.5499176845691437</v>
+        <v>0.5640676666272186</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.6400396146479227</v>
+        <v>0.6504910732185931</v>
       </c>
     </row>
     <row r="14">
@@ -3831,19 +3831,19 @@
         <v>6969</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>3521</v>
+        <v>3488</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>12225</v>
+        <v>12367</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.04513746320434478</v>
+        <v>0.03812681024071258</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.02280560973242308</v>
+        <v>0.01908119453245691</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.07917770724283928</v>
+        <v>0.06765586549315915</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>8</v>
@@ -3852,19 +3852,19 @@
         <v>4752</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2294</v>
+        <v>1872</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>9441</v>
+        <v>9187</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.03225119548991224</v>
+        <v>0.02781058664208085</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.01556580908622916</v>
+        <v>0.01095429694189903</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.06406996323017015</v>
+        <v>0.05376202229978598</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>18</v>
@@ -3873,19 +3873,19 @@
         <v>11721</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>7029</v>
+        <v>6818</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>17489</v>
+        <v>17641</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.03884491100576926</v>
+        <v>0.03314247845888387</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.02329432542783499</v>
+        <v>0.01927675949460233</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.05795804920084996</v>
+        <v>0.04987973320943385</v>
       </c>
     </row>
     <row r="15">
@@ -3896,16 +3896,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>154400</v>
+        <v>182791</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -3917,16 +3917,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>233</v>
+        <v>272</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>147348</v>
+        <v>170876</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -3938,16 +3938,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>460</v>
+        <v>541</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>301749</v>
+        <v>353667</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -3974,22 +3974,22 @@
         <v>18</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>11587</v>
+        <v>11586</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>7181</v>
+        <v>6970</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>17367</v>
+        <v>17921</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.09709169040659595</v>
+        <v>0.0786996294253992</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.06017203516981055</v>
+        <v>0.04733954693352043</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1455339325925479</v>
+        <v>0.1217243208050768</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>14</v>
@@ -3998,19 +3998,19 @@
         <v>8231</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>4624</v>
+        <v>4637</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>13136</v>
+        <v>13091</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.07384016270199144</v>
+        <v>0.06177871863677376</v>
       </c>
       <c r="O16" s="6" t="n">
-        <v>0.04148251714328698</v>
+        <v>0.03480033480267581</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.1178420610669313</v>
+        <v>0.09825497436793816</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>32</v>
@@ -4019,19 +4019,19 @@
         <v>19818</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>14055</v>
+        <v>14266</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>27100</v>
+        <v>27483</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.08586198913273393</v>
+        <v>0.07066114922676588</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.06089681266572342</v>
+        <v>0.05086591813599177</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.117415272278508</v>
+        <v>0.09799291638658973</v>
       </c>
     </row>
     <row r="17">
@@ -4042,67 +4042,67 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>18551</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>12443</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>26447</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>0.1260058847444143</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>0.08452009927881531</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>0.1796394197902775</v>
+      </c>
+      <c r="J17" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="D17" s="5" t="n">
-        <v>14597</v>
-      </c>
-      <c r="E17" s="5" t="n">
-        <v>9154</v>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>21515</v>
-      </c>
-      <c r="G17" s="6" t="n">
-        <v>0.1223207318166466</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>0.07670747286279514</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>0.1802883196953004</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>16</v>
-      </c>
       <c r="K17" s="5" t="n">
-        <v>9144</v>
+        <v>12076</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>5237</v>
+        <v>7848</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>14059</v>
+        <v>17778</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.08202523805640181</v>
+        <v>0.09063818278765171</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.04697918756421483</v>
+        <v>0.05890663090359344</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1261249126745377</v>
+        <v>0.1334343180595626</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>23741</v>
+        <v>30627</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>17483</v>
+        <v>22816</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>31179</v>
+        <v>39411</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.1028593715413512</v>
+        <v>0.1092040366995848</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.07574726394108162</v>
+        <v>0.0813509880077946</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1350876900777923</v>
+        <v>0.1405216492538614</v>
       </c>
     </row>
     <row r="18">
@@ -4113,67 +4113,67 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>16070</v>
+        <v>25998</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>10443</v>
+        <v>19625</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>22095</v>
+        <v>34452</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.1346579063109094</v>
+        <v>0.1765905351258311</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.08750709555858105</v>
+        <v>0.1333013012238761</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.1851505875523339</v>
+        <v>0.2340126778258337</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>20465</v>
+        <v>27775</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>14309</v>
+        <v>21048</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>27420</v>
+        <v>34785</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1835873578168418</v>
+        <v>0.2084609799279913</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1283621366660086</v>
+        <v>0.1579719375312645</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2459818192884048</v>
+        <v>0.2610802134721195</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>36534</v>
+        <v>53773</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>28803</v>
+        <v>42858</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>45702</v>
+        <v>64431</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.1582891760875068</v>
+        <v>0.1917309695069412</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1247933880223747</v>
+        <v>0.1528134292681652</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.1980077999082705</v>
+        <v>0.2297321793795676</v>
       </c>
     </row>
     <row r="19">
@@ -4184,67 +4184,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>65256</v>
+        <v>79261</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>56613</v>
+        <v>69111</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>74482</v>
+        <v>88965</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.546821825081838</v>
+        <v>0.5383700853559661</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.4744037690081954</v>
+        <v>0.4694292593570031</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.624137916425695</v>
+        <v>0.6042836232102302</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>65744</v>
+        <v>77265</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>57550</v>
+        <v>68736</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>73483</v>
+        <v>86564</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.5897770229196165</v>
+        <v>0.579911883229526</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.516270402993843</v>
+        <v>0.515897667332179</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.6592083033693297</v>
+        <v>0.6497023519486079</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>200</v>
+        <v>240</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>130999</v>
+        <v>156526</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>118371</v>
+        <v>142616</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>143290</v>
+        <v>169634</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.5675677324478461</v>
+        <v>0.5581050111997164</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.5128553037716519</v>
+        <v>0.5085075084846924</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.6208188756850102</v>
+        <v>0.6048417274567669</v>
       </c>
     </row>
     <row r="20">
@@ -4261,19 +4261,19 @@
         <v>11827</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>7233</v>
+        <v>7225</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>18579</v>
+        <v>18898</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.09910784638401009</v>
+        <v>0.08033386534838934</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.06060648191755116</v>
+        <v>0.04907272184934639</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1556883653557127</v>
+        <v>0.128358900346145</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>12</v>
@@ -4282,19 +4282,19 @@
         <v>7889</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>4476</v>
+        <v>4430</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>12943</v>
+        <v>13276</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.07077021850514836</v>
+        <v>0.05921023541805721</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.04015186095520078</v>
+        <v>0.03324981905770609</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1161139592440217</v>
+        <v>0.09964616053992155</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>28</v>
@@ -4303,19 +4303,19 @@
         <v>19716</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>13279</v>
+        <v>13235</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>27713</v>
+        <v>27938</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.08542173079056187</v>
+        <v>0.07029883336699168</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.05753118700476862</v>
+        <v>0.04718863615655546</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.1200708047141949</v>
+        <v>0.09961522359649858</v>
       </c>
     </row>
     <row r="21">
@@ -4326,16 +4326,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>119336</v>
+        <v>147224</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -4347,16 +4347,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>181</v>
+        <v>218</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>111472</v>
+        <v>133236</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -4368,16 +4368,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>355</v>
+        <v>433</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>230808</v>
+        <v>280460</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -4407,19 +4407,19 @@
         <v>14471</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>9585</v>
+        <v>9025</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>22370</v>
+        <v>21820</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.09501080506927234</v>
+        <v>0.08037392699151978</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.06293545873369777</v>
+        <v>0.05012766158930627</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.1468769587311233</v>
+        <v>0.1211944428967157</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>12</v>
@@ -4428,19 +4428,19 @@
         <v>8940</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>4542</v>
+        <v>5176</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>14660</v>
+        <v>15944</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.06321747697332278</v>
+        <v>0.05395300994903777</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.0321174851856319</v>
+        <v>0.03123771484108293</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.1036712155058696</v>
+        <v>0.09622503046643117</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>32</v>
@@ -4449,19 +4449,19 @@
         <v>23410</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>16492</v>
+        <v>16140</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>32506</v>
+        <v>32556</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.07970368268049076</v>
+        <v>0.06771164680823323</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.0561502778251471</v>
+        <v>0.04668451873192439</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.1106714569675513</v>
+        <v>0.09416489507551419</v>
       </c>
     </row>
     <row r="23">
@@ -4472,67 +4472,67 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>16454</v>
+        <v>18523</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>10768</v>
+        <v>12563</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>22861</v>
+        <v>26490</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.1080321788461448</v>
+        <v>0.102884438578682</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.07070204205485882</v>
+        <v>0.06977879982605599</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.1501035762605405</v>
+        <v>0.1471357107900761</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>11513</v>
+        <v>13630</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>7014</v>
+        <v>7791</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>18293</v>
+        <v>20138</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.08141625097118804</v>
+        <v>0.08225918085029288</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.04959884675210119</v>
+        <v>0.04702311280951522</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1293623769517719</v>
+        <v>0.1215376813740733</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>27967</v>
+        <v>32153</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>20249</v>
+        <v>23723</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>37032</v>
+        <v>40770</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.09521775236511056</v>
+        <v>0.09299974033791171</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.06894012723365822</v>
+        <v>0.06861649598375297</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1260798948471431</v>
+        <v>0.1179229842046953</v>
       </c>
     </row>
     <row r="24">
@@ -4543,67 +4543,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>42760</v>
+        <v>51465</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>34097</v>
+        <v>41307</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>52397</v>
+        <v>61813</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.2807545051268666</v>
+        <v>0.2858531274235004</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.2238718056543071</v>
+        <v>0.2294324035160705</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.3440262130654053</v>
+        <v>0.343327409629745</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>34907</v>
+        <v>39521</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>26625</v>
+        <v>30366</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>44534</v>
+        <v>49875</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.2468503047814733</v>
+        <v>0.2385208096575059</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.188282289428218</v>
+        <v>0.1832657429812756</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.3149279661571889</v>
+        <v>0.3010081327369756</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>77668</v>
+        <v>90986</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>64473</v>
+        <v>78016</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>89756</v>
+        <v>105469</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.2644310883831246</v>
+        <v>0.2631690143658912</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.2195066524192627</v>
+        <v>0.2256537587913548</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.3055892802768658</v>
+        <v>0.305059506413897</v>
       </c>
     </row>
     <row r="25">
@@ -4614,67 +4614,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>70310</v>
+        <v>87272</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>60082</v>
+        <v>76885</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>80735</v>
+        <v>99205</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.4616436785986043</v>
+        <v>0.4847347289641409</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.3944862394804139</v>
+        <v>0.4270466377265127</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.5300907995762115</v>
+        <v>0.5510164495359414</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>112</v>
+        <v>136</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>82490</v>
+        <v>100042</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>72290</v>
+        <v>89124</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>92413</v>
+        <v>111298</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.5833321697030867</v>
+        <v>0.6037738659043079</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.5112041222192866</v>
+        <v>0.5378825941821664</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.653508531378399</v>
+        <v>0.671708849393312</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>211</v>
+        <v>260</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>152800</v>
+        <v>187313</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>137920</v>
+        <v>173021</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>166147</v>
+        <v>204216</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.5202314622059384</v>
+        <v>0.541784486256419</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.4695676904015403</v>
+        <v>0.5004456274149853</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.5656738818124695</v>
+        <v>0.5906725081934773</v>
       </c>
     </row>
     <row r="26">
@@ -4691,19 +4691,19 @@
         <v>8310</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>4264</v>
+        <v>4449</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>13909</v>
+        <v>14525</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.05455883235911201</v>
+        <v>0.04615377804215694</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.02799540836697042</v>
+        <v>0.02471190807083742</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.09132486879861614</v>
+        <v>0.08067501234876746</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>5</v>
@@ -4712,19 +4712,19 @@
         <v>3561</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>7913</v>
+        <v>8406</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.02518379757092922</v>
+        <v>0.02149313363885551</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.009844417250018046</v>
+        <v>0.008393129080160801</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.05595949558859191</v>
+        <v>0.05073474980525321</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>16</v>
@@ -4733,19 +4733,19 @@
         <v>11871</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>7075</v>
+        <v>6966</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>18955</v>
+        <v>19309</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.04041601436533567</v>
+        <v>0.03433511223154487</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.02408798371464246</v>
+        <v>0.02014883276604785</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.06453436201268878</v>
+        <v>0.05584985318635299</v>
       </c>
     </row>
     <row r="27">
@@ -4756,16 +4756,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>152304</v>
+        <v>180040</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -4777,16 +4777,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>190</v>
+        <v>224</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>141411</v>
+        <v>165694</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -4798,16 +4798,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>403</v>
+        <v>477</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>293716</v>
+        <v>345734</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -4837,19 +4837,19 @@
         <v>49893</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>40373</v>
+        <v>39257</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>62860</v>
+        <v>61263</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.09517553857995151</v>
+        <v>0.0790071602179829</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.07701526912698325</v>
+        <v>0.0621653092029538</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.1199111714694741</v>
+        <v>0.09701254255830065</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>45</v>
@@ -4858,19 +4858,19 @@
         <v>28947</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>21942</v>
+        <v>21330</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>38638</v>
+        <v>37770</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.05941582670356314</v>
+        <v>0.05012595175945889</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.04503704017761716</v>
+        <v>0.03693643464520396</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.07930639473648537</v>
+        <v>0.06540279238725248</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>117</v>
@@ -4879,19 +4879,19 @@
         <v>78840</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>65138</v>
+        <v>66489</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>94282</v>
+        <v>94830</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.07795015668913016</v>
+        <v>0.06521164604088794</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.06440288371088079</v>
+        <v>0.05499520384656755</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.09321717571063129</v>
+        <v>0.07843698128650946</v>
       </c>
     </row>
     <row r="29">
@@ -4902,67 +4902,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>62674</v>
+        <v>78089</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>51193</v>
+        <v>64799</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>75448</v>
+        <v>93247</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1195570572329769</v>
+        <v>0.1236559899370605</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09765447306179886</v>
+        <v>0.1026112336879394</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1439241473673319</v>
+        <v>0.1476601083961345</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>38866</v>
+        <v>45116</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>29688</v>
+        <v>35743</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>49259</v>
+        <v>55714</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07977506961950961</v>
+        <v>0.07812431973573913</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.06093624757692553</v>
+        <v>0.06189315751584948</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1011070846613938</v>
+        <v>0.09647590010222286</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>101541</v>
+        <v>123205</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>86375</v>
+        <v>106465</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>117697</v>
+        <v>140019</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1003941531417287</v>
+        <v>0.101907149244636</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.08539951592246428</v>
+        <v>0.08806077074210729</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1163683341045885</v>
+        <v>0.115814276570345</v>
       </c>
     </row>
     <row r="30">
@@ -4973,67 +4973,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>177</v>
+        <v>222</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>125233</v>
+        <v>156079</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>110034</v>
+        <v>140160</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>140312</v>
+        <v>174687</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.23889425466918</v>
+        <v>0.2471556176340138</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.2099005159746317</v>
+        <v>0.2219472729403012</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.2676580452636066</v>
+        <v>0.2766229547962112</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>148</v>
+        <v>181</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>101672</v>
+        <v>122865</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>87514</v>
+        <v>107239</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>116604</v>
+        <v>139031</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.2086876950611254</v>
+        <v>0.2127557961254483</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1796266552291893</v>
+        <v>0.1856983703716776</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.239335498468346</v>
+        <v>0.2407488064247911</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>325</v>
+        <v>403</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>226906</v>
+        <v>278944</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>205350</v>
+        <v>257609</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>249456</v>
+        <v>305661</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.2243438151506738</v>
+        <v>0.2307240605545215</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.2030314735056603</v>
+        <v>0.2130775566749106</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2466391477760726</v>
+        <v>0.2528231540567366</v>
       </c>
     </row>
     <row r="31">
@@ -5044,67 +5044,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>364</v>
+        <v>450</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>254976</v>
+        <v>315995</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>235846</v>
+        <v>296682</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>272198</v>
+        <v>336092</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.4863894319041682</v>
+        <v>0.5003875219920444</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4498971789407189</v>
+        <v>0.469805520337693</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5192433282162127</v>
+        <v>0.5322118045669378</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>445</v>
+        <v>540</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>298703</v>
+        <v>361554</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>281624</v>
+        <v>342785</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>315262</v>
+        <v>380221</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6131033684668857</v>
+        <v>0.6260765010018331</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.5780478453230969</v>
+        <v>0.5935761286545423</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.6470898548161683</v>
+        <v>0.6584007070238873</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>809</v>
+        <v>990</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>553679</v>
+        <v>677549</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>528303</v>
+        <v>650816</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>579459</v>
+        <v>708883</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.5474272824250871</v>
+        <v>0.5604246251598093</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.5223376615531508</v>
+        <v>0.53831271524308</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.5729154089105897</v>
+        <v>0.5863415003871727</v>
       </c>
     </row>
     <row r="32">
@@ -5121,19 +5121,19 @@
         <v>31445</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>23399</v>
+        <v>22996</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>41548</v>
+        <v>42177</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.05998371761372345</v>
+        <v>0.0497937102188984</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.04463589268295169</v>
+        <v>0.03641539584030222</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.07925688276476886</v>
+        <v>0.06678878240000873</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>29</v>
@@ -5142,19 +5142,19 @@
         <v>19010</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>13339</v>
+        <v>13002</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>26892</v>
+        <v>26864</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.03901804014891608</v>
+        <v>0.03291743137752063</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02737838002734913</v>
+        <v>0.02251391871343842</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.05519763710299874</v>
+        <v>0.04651842499133328</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>72</v>
@@ -5163,19 +5163,19 @@
         <v>50454</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>40692</v>
+        <v>39663</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>62231</v>
+        <v>63180</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.04988459259338034</v>
+        <v>0.04173251900014519</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.0402323219481169</v>
+        <v>0.03280642049981401</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.06152805684246164</v>
+        <v>0.05225813357009278</v>
       </c>
     </row>
     <row r="33">
@@ -5186,16 +5186,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>745</v>
+        <v>897</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>524221</v>
+        <v>631500</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -5207,16 +5207,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>726</v>
+        <v>864</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>487199</v>
+        <v>577492</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -5228,16 +5228,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>1471</v>
+        <v>1761</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>1011421</v>
+        <v>1208993</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
@@ -5309,7 +5309,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 78,24%)</t>
+          <t>Menores según la categoría de IMC recogido por medición en 2023 (tasa de respuesta: 82,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5499,19 +5499,19 @@
         <v>3255</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1324</v>
+        <v>1400</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>6237</v>
+        <v>6214</v>
       </c>
       <c r="G4" s="6" t="n">
-        <v>0.06012672164370838</v>
+        <v>0.05545785776324366</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.02445693721067462</v>
+        <v>0.02384386484318696</v>
       </c>
       <c r="I4" s="6" t="n">
-        <v>0.1152009264784523</v>
+        <v>0.1058703959158015</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>6</v>
@@ -5520,40 +5520,40 @@
         <v>2469</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>5104</v>
+        <v>5382</v>
       </c>
       <c r="N4" s="6" t="n">
-        <v>0.06045842337303578</v>
+        <v>0.05654266480442362</v>
       </c>
       <c r="O4" s="6" t="n">
-        <v>0.02578574074125103</v>
+        <v>0.02426751274691854</v>
       </c>
       <c r="P4" s="6" t="n">
-        <v>0.1249716659494771</v>
+        <v>0.1232390195294402</v>
       </c>
       <c r="Q4" s="5" t="n">
         <v>14</v>
       </c>
       <c r="R4" s="5" t="n">
-        <v>5725</v>
+        <v>5724</v>
       </c>
       <c r="S4" s="5" t="n">
-        <v>3370</v>
+        <v>3230</v>
       </c>
       <c r="T4" s="5" t="n">
-        <v>9864</v>
+        <v>9574</v>
       </c>
       <c r="U4" s="6" t="n">
-        <v>0.06026934843036701</v>
+        <v>0.05592062426811589</v>
       </c>
       <c r="V4" s="6" t="n">
-        <v>0.03547650082394224</v>
+        <v>0.03155203437065274</v>
       </c>
       <c r="W4" s="6" t="n">
-        <v>0.1038487542390662</v>
+        <v>0.09352299111928275</v>
       </c>
     </row>
     <row r="5">
@@ -5570,61 +5570,61 @@
         <v>5559</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>2280</v>
+        <v>2463</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>10775</v>
+        <v>10770</v>
       </c>
       <c r="G5" s="6" t="n">
-        <v>0.1026811270773141</v>
+        <v>0.09470789666808818</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.04211917590813015</v>
+        <v>0.04195384197695182</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>0.1990230145277495</v>
+        <v>0.1834853346979812</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>4735</v>
+        <v>5241</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>2132</v>
+        <v>2733</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>8141</v>
+        <v>8754</v>
       </c>
       <c r="N5" s="6" t="n">
-        <v>0.1159288462488428</v>
+        <v>0.1200096425296689</v>
       </c>
       <c r="O5" s="6" t="n">
-        <v>0.05219818013538214</v>
+        <v>0.06259322908018904</v>
       </c>
       <c r="P5" s="6" t="n">
-        <v>0.1993455713850391</v>
+        <v>0.2004662312530834</v>
       </c>
       <c r="Q5" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R5" s="5" t="n">
-        <v>10294</v>
+        <v>10800</v>
       </c>
       <c r="S5" s="5" t="n">
-        <v>6255</v>
+        <v>6477</v>
       </c>
       <c r="T5" s="5" t="n">
-        <v>16165</v>
+        <v>16351</v>
       </c>
       <c r="U5" s="6" t="n">
-        <v>0.1083774483470955</v>
+        <v>0.1055013373953839</v>
       </c>
       <c r="V5" s="6" t="n">
-        <v>0.06585916620045698</v>
+        <v>0.06326713877018435</v>
       </c>
       <c r="W5" s="6" t="n">
-        <v>0.1701883272805365</v>
+        <v>0.1597248308416169</v>
       </c>
     </row>
     <row r="6">
@@ -5635,67 +5635,67 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>17582</v>
+        <v>20870</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>11981</v>
+        <v>14517</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>24229</v>
+        <v>28103</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>0.3247414208251734</v>
+        <v>0.355550375568607</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>0.2212962197173176</v>
+        <v>0.2473058208451522</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>0.4475142453867505</v>
+        <v>0.4787635421306318</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>5371</v>
+        <v>6254</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>2486</v>
+        <v>3269</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>9095</v>
+        <v>10572</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.1315160554015423</v>
+        <v>0.1432069855686318</v>
       </c>
       <c r="O6" s="6" t="n">
-        <v>0.06086212585114449</v>
+        <v>0.07486855861612347</v>
       </c>
       <c r="P6" s="6" t="n">
-        <v>0.222682532205832</v>
+        <v>0.2421044343719354</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="R6" s="5" t="n">
-        <v>22953</v>
+        <v>27124</v>
       </c>
       <c r="S6" s="5" t="n">
-        <v>15927</v>
+        <v>18890</v>
       </c>
       <c r="T6" s="5" t="n">
-        <v>31137</v>
+        <v>35574</v>
       </c>
       <c r="U6" s="6" t="n">
-        <v>0.241657401253758</v>
+        <v>0.2649670693281501</v>
       </c>
       <c r="V6" s="6" t="n">
-        <v>0.1676872841405057</v>
+        <v>0.1845317826242447</v>
       </c>
       <c r="W6" s="6" t="n">
-        <v>0.3278176153496251</v>
+        <v>0.3475087642619704</v>
       </c>
     </row>
     <row r="7">
@@ -5706,67 +5706,67 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>25363</v>
+        <v>26633</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>19366</v>
+        <v>19732</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>31510</v>
+        <v>33765</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.4684691948050827</v>
+        <v>0.4537175181096443</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.3576945494711864</v>
+        <v>0.3361536026240034</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>0.5819952734471155</v>
+        <v>0.5752173843608966</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>27179</v>
+        <v>28618</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>22755</v>
+        <v>23571</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>31166</v>
+        <v>33115</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>0.6654740646056246</v>
+        <v>0.6553423844080503</v>
       </c>
       <c r="O7" s="6" t="n">
-        <v>0.5571638679376453</v>
+        <v>0.5397592151374813</v>
       </c>
       <c r="P7" s="6" t="n">
-        <v>0.7631164058891011</v>
+        <v>0.7583283931270192</v>
       </c>
       <c r="Q7" s="5" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="R7" s="5" t="n">
-        <v>52542</v>
+        <v>55251</v>
       </c>
       <c r="S7" s="5" t="n">
-        <v>43834</v>
+        <v>46996</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>61169</v>
+        <v>65082</v>
       </c>
       <c r="U7" s="6" t="n">
-        <v>0.5531783447776389</v>
+        <v>0.5397284224735702</v>
       </c>
       <c r="V7" s="6" t="n">
-        <v>0.4614999084659989</v>
+        <v>0.4590859411530535</v>
       </c>
       <c r="W7" s="6" t="n">
-        <v>0.6440098289082801</v>
+        <v>0.6357644620146945</v>
       </c>
     </row>
     <row r="8">
@@ -5783,19 +5783,19 @@
         <v>2381</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>5646</v>
+        <v>6074</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.04398153564872129</v>
+        <v>0.04056635189041682</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.01222311728283787</v>
+        <v>0.01110178084747344</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>0.1042762103879149</v>
+        <v>0.1034801809040962</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>2</v>
@@ -5807,37 +5807,37 @@
         <v>0</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>3375</v>
+        <v>3622</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>0.02662261037095452</v>
+        <v>0.02489832268922542</v>
       </c>
       <c r="O8" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P8" s="6" t="n">
-        <v>0.08264301275867349</v>
+        <v>0.08294440526781059</v>
       </c>
       <c r="Q8" s="5" t="n">
         <v>6</v>
       </c>
       <c r="R8" s="5" t="n">
-        <v>3469</v>
+        <v>3468</v>
       </c>
       <c r="S8" s="5" t="n">
-        <v>1459</v>
+        <v>1200</v>
       </c>
       <c r="T8" s="5" t="n">
-        <v>7670</v>
+        <v>6796</v>
       </c>
       <c r="U8" s="6" t="n">
-        <v>0.03651745719114045</v>
+        <v>0.03388254653477986</v>
       </c>
       <c r="V8" s="6" t="n">
-        <v>0.01535945141218058</v>
+        <v>0.01171900209460668</v>
       </c>
       <c r="W8" s="6" t="n">
-        <v>0.08075497931256569</v>
+        <v>0.06639137675156029</v>
       </c>
     </row>
     <row r="9">
@@ -5848,16 +5848,16 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>54141</v>
+        <v>58699</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>1</v>
@@ -5869,16 +5869,16 @@
         <v>1</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>40841</v>
+        <v>43669</v>
       </c>
       <c r="N9" s="6" t="n">
         <v>1</v>
@@ -5890,16 +5890,16 @@
         <v>1</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="R9" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="S9" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="T9" s="5" t="n">
-        <v>94982</v>
+        <v>102368</v>
       </c>
       <c r="U9" s="6" t="n">
         <v>1</v>
@@ -5929,19 +5929,19 @@
         <v>11274</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>6527</v>
+        <v>6846</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>17127</v>
+        <v>17315</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.1084212635269964</v>
+        <v>0.1042765134412386</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>0.06276717216025024</v>
+        <v>0.06331571072771396</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>0.1647057533146778</v>
+        <v>0.1601472276012166</v>
       </c>
       <c r="J10" s="5" t="n">
         <v>6</v>
@@ -5950,19 +5950,19 @@
         <v>3475</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>1367</v>
+        <v>1354</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>7460</v>
+        <v>7632</v>
       </c>
       <c r="N10" s="6" t="n">
-        <v>0.05151059604832708</v>
+        <v>0.04963387503310774</v>
       </c>
       <c r="O10" s="6" t="n">
-        <v>0.0202562323298656</v>
+        <v>0.019336136070436</v>
       </c>
       <c r="P10" s="6" t="n">
-        <v>0.1105812038627658</v>
+        <v>0.1090145132147485</v>
       </c>
       <c r="Q10" s="5" t="n">
         <v>24</v>
@@ -5971,19 +5971,19 @@
         <v>14749</v>
       </c>
       <c r="S10" s="5" t="n">
-        <v>9941</v>
+        <v>9370</v>
       </c>
       <c r="T10" s="5" t="n">
-        <v>21785</v>
+        <v>21513</v>
       </c>
       <c r="U10" s="6" t="n">
-        <v>0.08602770157852337</v>
+        <v>0.08279969405879332</v>
       </c>
       <c r="V10" s="6" t="n">
-        <v>0.05798192972490435</v>
+        <v>0.05260178091788853</v>
       </c>
       <c r="W10" s="6" t="n">
-        <v>0.1270676553388222</v>
+        <v>0.1207702362651676</v>
       </c>
     </row>
     <row r="11">
@@ -6000,61 +6000,61 @@
         <v>17309</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>11577</v>
+        <v>11230</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>26052</v>
+        <v>25485</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.1664556323569865</v>
+        <v>0.160092332631055</v>
       </c>
       <c r="H11" s="6" t="n">
-        <v>0.1113338802679592</v>
+        <v>0.1038728179220501</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>0.2505388008793886</v>
+        <v>0.2357134147345918</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>3055</v>
+        <v>3625</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>1097</v>
+        <v>1455</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>7396</v>
+        <v>7854</v>
       </c>
       <c r="N11" s="6" t="n">
-        <v>0.04529084413177817</v>
+        <v>0.05177173845567749</v>
       </c>
       <c r="O11" s="6" t="n">
-        <v>0.0162565522914191</v>
+        <v>0.020781784372127</v>
       </c>
       <c r="P11" s="6" t="n">
-        <v>0.109635831060921</v>
+        <v>0.1121739433043805</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R11" s="5" t="n">
-        <v>20364</v>
+        <v>20933</v>
       </c>
       <c r="S11" s="5" t="n">
-        <v>13081</v>
+        <v>14321</v>
       </c>
       <c r="T11" s="5" t="n">
-        <v>29145</v>
+        <v>29607</v>
       </c>
       <c r="U11" s="6" t="n">
-        <v>0.1187789609822957</v>
+        <v>0.1175178540868862</v>
       </c>
       <c r="V11" s="6" t="n">
-        <v>0.07629869768229469</v>
+        <v>0.08039546747415909</v>
       </c>
       <c r="W11" s="6" t="n">
-        <v>0.1699964233458547</v>
+        <v>0.1662113303825689</v>
       </c>
     </row>
     <row r="12">
@@ -6065,67 +6065,67 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>22064</v>
+        <v>22624</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>14145</v>
+        <v>15375</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>34039</v>
+        <v>35552</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.2121921935589803</v>
+        <v>0.2092552855895909</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>0.1360312727283809</v>
+        <v>0.1422034178907499</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>0.3273502192429836</v>
+        <v>0.328828734805905</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>12570</v>
+        <v>13006</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>7985</v>
+        <v>8310</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>18979</v>
+        <v>18564</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.1863253781901978</v>
+        <v>0.1857699607060197</v>
       </c>
       <c r="O12" s="6" t="n">
-        <v>0.118370696633343</v>
+        <v>0.1186877352999102</v>
       </c>
       <c r="P12" s="6" t="n">
-        <v>0.2813398161487312</v>
+        <v>0.2651537823540107</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="R12" s="5" t="n">
-        <v>34634</v>
+        <v>35630</v>
       </c>
       <c r="S12" s="5" t="n">
-        <v>26372</v>
+        <v>26476</v>
       </c>
       <c r="T12" s="5" t="n">
-        <v>48917</v>
+        <v>47881</v>
       </c>
       <c r="U12" s="6" t="n">
-        <v>0.2020139588266666</v>
+        <v>0.2000245804963417</v>
       </c>
       <c r="V12" s="6" t="n">
-        <v>0.1538212153831348</v>
+        <v>0.1486351329643707</v>
       </c>
       <c r="W12" s="6" t="n">
-        <v>0.2853212194283143</v>
+        <v>0.2687987691897942</v>
       </c>
     </row>
     <row r="13">
@@ -6136,67 +6136,67 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>48642</v>
+        <v>52216</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>38848</v>
+        <v>41833</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>57778</v>
+        <v>61215</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.4677901065957936</v>
+        <v>0.4829607162001693</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>0.3735964548183537</v>
+        <v>0.3869244245766446</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>0.5556438017394836</v>
+        <v>0.5661930836871671</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>43048</v>
+        <v>44593</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>36496</v>
+        <v>38097</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>49493</v>
+        <v>51035</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.6381124103229426</v>
+        <v>0.6369331999128947</v>
       </c>
       <c r="O13" s="6" t="n">
-        <v>0.540989590223719</v>
+        <v>0.5441513714975615</v>
       </c>
       <c r="P13" s="6" t="n">
-        <v>0.7336577875068139</v>
+        <v>0.7289481382015719</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="R13" s="5" t="n">
-        <v>91690</v>
+        <v>96809</v>
       </c>
       <c r="S13" s="5" t="n">
-        <v>79302</v>
+        <v>84506</v>
       </c>
       <c r="T13" s="5" t="n">
-        <v>102859</v>
+        <v>109161</v>
       </c>
       <c r="U13" s="6" t="n">
-        <v>0.5348095816555462</v>
+        <v>0.5434782775570279</v>
       </c>
       <c r="V13" s="6" t="n">
-        <v>0.4625513288638413</v>
+        <v>0.4744116514565392</v>
       </c>
       <c r="W13" s="6" t="n">
-        <v>0.5999511671901887</v>
+        <v>0.6128218870015828</v>
       </c>
     </row>
     <row r="14">
@@ -6213,19 +6213,19 @@
         <v>4694</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>1907</v>
+        <v>1886</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>9322</v>
+        <v>8973</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.04514080396124315</v>
+        <v>0.04341515213794605</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>0.01834193989514105</v>
+        <v>0.0174434828439978</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>0.08965281621513646</v>
+        <v>0.08299789353633555</v>
       </c>
       <c r="J14" s="5" t="n">
         <v>8</v>
@@ -6234,19 +6234,19 @@
         <v>5313</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2324</v>
+        <v>2312</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>9915</v>
+        <v>9980</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.07876077130675441</v>
+        <v>0.07589122589230041</v>
       </c>
       <c r="O14" s="6" t="n">
-        <v>0.03445412414796494</v>
+        <v>0.03301848799436957</v>
       </c>
       <c r="P14" s="6" t="n">
-        <v>0.1469708428808919</v>
+        <v>0.1425494963572773</v>
       </c>
       <c r="Q14" s="5" t="n">
         <v>15</v>
@@ -6255,19 +6255,19 @@
         <v>10007</v>
       </c>
       <c r="S14" s="5" t="n">
-        <v>5666</v>
+        <v>5637</v>
       </c>
       <c r="T14" s="5" t="n">
-        <v>15820</v>
+        <v>16202</v>
       </c>
       <c r="U14" s="6" t="n">
-        <v>0.05836979695696808</v>
+        <v>0.05617959380095065</v>
       </c>
       <c r="V14" s="6" t="n">
-        <v>0.03305103081438484</v>
+        <v>0.03164845081664056</v>
       </c>
       <c r="W14" s="6" t="n">
-        <v>0.09227217141272123</v>
+        <v>0.09095711409928998</v>
       </c>
     </row>
     <row r="15">
@@ -6278,16 +6278,16 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>103983</v>
+        <v>108117</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>1</v>
@@ -6299,16 +6299,16 @@
         <v>1</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>67461</v>
+        <v>70012</v>
       </c>
       <c r="N15" s="6" t="n">
         <v>1</v>
@@ -6320,16 +6320,16 @@
         <v>1</v>
       </c>
       <c r="Q15" s="5" t="n">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="R15" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="S15" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="T15" s="5" t="n">
-        <v>171445</v>
+        <v>178128</v>
       </c>
       <c r="U15" s="6" t="n">
         <v>1</v>
@@ -6359,19 +6359,19 @@
         <v>3351</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>992</v>
+        <v>1013</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>7944</v>
+        <v>7687</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.04794008849984523</v>
+        <v>0.04728276512041102</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>0.01419485290211534</v>
+        <v>0.01429683147935078</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>0.1136644758689841</v>
+        <v>0.1084776726685088</v>
       </c>
       <c r="J16" s="5" t="n">
         <v>2</v>
@@ -6383,16 +6383,16 @@
         <v>0</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>4105</v>
+        <v>4163</v>
       </c>
       <c r="N16" s="6" t="n">
-        <v>0.01838063884595781</v>
+        <v>0.01743294307351928</v>
       </c>
       <c r="O16" s="6" t="n">
         <v>0</v>
       </c>
       <c r="P16" s="6" t="n">
-        <v>0.07440379079194748</v>
+        <v>0.07157537606150717</v>
       </c>
       <c r="Q16" s="5" t="n">
         <v>7</v>
@@ -6401,19 +6401,19 @@
         <v>4365</v>
       </c>
       <c r="S16" s="5" t="n">
-        <v>1863</v>
+        <v>1855</v>
       </c>
       <c r="T16" s="5" t="n">
-        <v>9161</v>
+        <v>9216</v>
       </c>
       <c r="U16" s="6" t="n">
-        <v>0.03490081878459991</v>
+        <v>0.03382682198472408</v>
       </c>
       <c r="V16" s="6" t="n">
-        <v>0.01490005559815473</v>
+        <v>0.01437815056416585</v>
       </c>
       <c r="W16" s="6" t="n">
-        <v>0.07325010548693218</v>
+        <v>0.07142447450574078</v>
       </c>
     </row>
     <row r="17">
@@ -6430,61 +6430,61 @@
         <v>6067</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2880</v>
+        <v>2978</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>11973</v>
+        <v>12237</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.08680756121423364</v>
+        <v>0.08561731227470641</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>0.04119870685490226</v>
+        <v>0.04202808882800925</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>0.1712994072840676</v>
+        <v>0.1726721855930239</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>4668</v>
+        <v>5491</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>1923</v>
+        <v>2397</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>10049</v>
+        <v>10505</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>0.08461779299034242</v>
+        <v>0.09440146026441609</v>
       </c>
       <c r="O17" s="6" t="n">
-        <v>0.03486208416150016</v>
+        <v>0.04120405479199643</v>
       </c>
       <c r="P17" s="6" t="n">
-        <v>0.1821634248120245</v>
+        <v>0.1806115040534474</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R17" s="5" t="n">
-        <v>10735</v>
+        <v>11558</v>
       </c>
       <c r="S17" s="5" t="n">
-        <v>5852</v>
+        <v>7029</v>
       </c>
       <c r="T17" s="5" t="n">
-        <v>17591</v>
+        <v>18557</v>
       </c>
       <c r="U17" s="6" t="n">
-        <v>0.085841610263877</v>
+        <v>0.08957710123623894</v>
       </c>
       <c r="V17" s="6" t="n">
-        <v>0.04679441006787886</v>
+        <v>0.05447234905915814</v>
       </c>
       <c r="W17" s="6" t="n">
-        <v>0.1406557770011008</v>
+        <v>0.1438172788650698</v>
       </c>
     </row>
     <row r="18">
@@ -6501,61 +6501,61 @@
         <v>13530</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>8483</v>
+        <v>8453</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>20427</v>
+        <v>21032</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.1935741240672857</v>
+        <v>0.1909199613115508</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>0.1213666793643946</v>
+        <v>0.1192803559650222</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>0.2922558968122472</v>
+        <v>0.2967888455971782</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>9611</v>
+        <v>10349</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>5648</v>
+        <v>6151</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>15548</v>
+        <v>16023</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>0.1742157527261364</v>
+        <v>0.1779237023162051</v>
       </c>
       <c r="O18" s="6" t="n">
-        <v>0.1023840244108307</v>
+        <v>0.1057428420166178</v>
       </c>
       <c r="P18" s="6" t="n">
-        <v>0.2818370123239964</v>
+        <v>0.2754696471933533</v>
       </c>
       <c r="Q18" s="5" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="R18" s="5" t="n">
-        <v>23141</v>
+        <v>23879</v>
       </c>
       <c r="S18" s="5" t="n">
-        <v>16024</v>
+        <v>16872</v>
       </c>
       <c r="T18" s="5" t="n">
-        <v>31861</v>
+        <v>33094</v>
       </c>
       <c r="U18" s="6" t="n">
-        <v>0.1850347558408571</v>
+        <v>0.1850614030346099</v>
       </c>
       <c r="V18" s="6" t="n">
-        <v>0.1281303167879875</v>
+        <v>0.1307545577384256</v>
       </c>
       <c r="W18" s="6" t="n">
-        <v>0.2547620636758341</v>
+        <v>0.2564755246406493</v>
       </c>
     </row>
     <row r="19">
@@ -6566,67 +6566,67 @@
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>43355</v>
+        <v>44327</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>35724</v>
+        <v>36951</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>50268</v>
+        <v>51412</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.6202984823728676</v>
+        <v>0.6255047031486961</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>0.5111096934243793</v>
+        <v>0.5214245590169707</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>0.7192097415651089</v>
+        <v>0.7254820487776328</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>37185</v>
+        <v>38623</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>30442</v>
+        <v>32012</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>42700</v>
+        <v>44131</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>0.674043353033138</v>
+        <v>0.6640125668735789</v>
       </c>
       <c r="O19" s="6" t="n">
-        <v>0.5518101661469429</v>
+        <v>0.5503506461949348</v>
       </c>
       <c r="P19" s="6" t="n">
-        <v>0.7740109381831305</v>
+        <v>0.7587159366763595</v>
       </c>
       <c r="Q19" s="5" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="R19" s="5" t="n">
-        <v>80540</v>
+        <v>82950</v>
       </c>
       <c r="S19" s="5" t="n">
-        <v>70500</v>
+        <v>73400</v>
       </c>
       <c r="T19" s="5" t="n">
-        <v>90114</v>
+        <v>92165</v>
       </c>
       <c r="U19" s="6" t="n">
-        <v>0.6440064293257323</v>
+        <v>0.6428635880273</v>
       </c>
       <c r="V19" s="6" t="n">
-        <v>0.5637260218090723</v>
+        <v>0.5688513735032381</v>
       </c>
       <c r="W19" s="6" t="n">
-        <v>0.720561630906162</v>
+        <v>0.7142830000544528</v>
       </c>
     </row>
     <row r="20">
@@ -6643,19 +6643,19 @@
         <v>3591</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>1115</v>
+        <v>1268</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>8060</v>
+        <v>8453</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.05137974384576796</v>
+        <v>0.05067525814463553</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01595916320661645</v>
+        <v>0.01789644341090514</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.1153110566742224</v>
+        <v>0.1192883007048803</v>
       </c>
       <c r="J20" s="5" t="n">
         <v>4</v>
@@ -6664,19 +6664,19 @@
         <v>2689</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>781</v>
+        <v>652</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>6685</v>
+        <v>6018</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>0.04874246240442569</v>
+        <v>0.04622932747228069</v>
       </c>
       <c r="O20" s="6" t="n">
-        <v>0.01415011167487315</v>
+        <v>0.01120650185929195</v>
       </c>
       <c r="P20" s="6" t="n">
-        <v>0.1211782354773975</v>
+        <v>0.1034653461787674</v>
       </c>
       <c r="Q20" s="5" t="n">
         <v>9</v>
@@ -6685,19 +6685,19 @@
         <v>6280</v>
       </c>
       <c r="S20" s="5" t="n">
-        <v>2764</v>
+        <v>2864</v>
       </c>
       <c r="T20" s="5" t="n">
-        <v>12135</v>
+        <v>11732</v>
       </c>
       <c r="U20" s="6" t="n">
-        <v>0.05021638578493375</v>
+        <v>0.04867108571712712</v>
       </c>
       <c r="V20" s="6" t="n">
-        <v>0.02210036943216948</v>
+        <v>0.02219929704831218</v>
       </c>
       <c r="W20" s="6" t="n">
-        <v>0.09703391754174792</v>
+        <v>0.09092628682611086</v>
       </c>
     </row>
     <row r="21">
@@ -6708,16 +6708,16 @@
         </is>
       </c>
       <c r="C21" s="5" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>69894</v>
+        <v>70866</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>1</v>
@@ -6729,16 +6729,16 @@
         <v>1</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>55167</v>
+        <v>58166</v>
       </c>
       <c r="N21" s="6" t="n">
         <v>1</v>
@@ -6750,16 +6750,16 @@
         <v>1</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="R21" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="S21" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="T21" s="5" t="n">
-        <v>125061</v>
+        <v>129032</v>
       </c>
       <c r="U21" s="6" t="n">
         <v>1</v>
@@ -6789,19 +6789,19 @@
         <v>2654</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>1046</v>
+        <v>932</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>6304</v>
+        <v>5837</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.03944234624786767</v>
+        <v>0.03674220162595888</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.015546340951187</v>
+        <v>0.01289473258119375</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.09367852395671107</v>
+        <v>0.08079211946439975</v>
       </c>
       <c r="J22" s="5" t="n">
         <v>4</v>
@@ -6810,19 +6810,19 @@
         <v>2864</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>988</v>
+        <v>628</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>6928</v>
+        <v>7364</v>
       </c>
       <c r="N22" s="6" t="n">
-        <v>0.03936596379330932</v>
+        <v>0.03729243499602426</v>
       </c>
       <c r="O22" s="6" t="n">
-        <v>0.01358548456744493</v>
+        <v>0.008177274500088589</v>
       </c>
       <c r="P22" s="6" t="n">
-        <v>0.09522652756219857</v>
+        <v>0.09589699803851801</v>
       </c>
       <c r="Q22" s="5" t="n">
         <v>9</v>
@@ -6831,19 +6831,19 @@
         <v>5518</v>
       </c>
       <c r="S22" s="5" t="n">
-        <v>2650</v>
+        <v>2499</v>
       </c>
       <c r="T22" s="5" t="n">
-        <v>11039</v>
+        <v>10288</v>
       </c>
       <c r="U22" s="6" t="n">
-        <v>0.03940266773342313</v>
+        <v>0.03702572364650006</v>
       </c>
       <c r="V22" s="6" t="n">
-        <v>0.01892037154876737</v>
+        <v>0.01676450527005933</v>
       </c>
       <c r="W22" s="6" t="n">
-        <v>0.07882587271541347</v>
+        <v>0.06903059626970172</v>
       </c>
     </row>
     <row r="23">
@@ -6854,25 +6854,25 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>9469</v>
+        <v>9924</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4854</v>
+        <v>5556</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>16590</v>
+        <v>16506</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.140699779519066</v>
+        <v>0.1373686279364064</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>0.07213196586564527</v>
+        <v>0.07690412675826379</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>0.2465164860344169</v>
+        <v>0.2284865439505537</v>
       </c>
       <c r="J23" s="5" t="n">
         <v>8</v>
@@ -6881,40 +6881,40 @@
         <v>5358</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>2528</v>
+        <v>2504</v>
       </c>
       <c r="M23" s="5" t="n">
-        <v>9731</v>
+        <v>9887</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>0.07365298747993812</v>
+        <v>0.06977345359255277</v>
       </c>
       <c r="O23" s="6" t="n">
-        <v>0.03475069520964782</v>
+        <v>0.03260014686789023</v>
       </c>
       <c r="P23" s="6" t="n">
-        <v>0.1337647937529948</v>
+        <v>0.1287441370111849</v>
       </c>
       <c r="Q23" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R23" s="5" t="n">
-        <v>14827</v>
+        <v>15282</v>
       </c>
       <c r="S23" s="5" t="n">
-        <v>8865</v>
+        <v>9671</v>
       </c>
       <c r="T23" s="5" t="n">
-        <v>22778</v>
+        <v>23559</v>
       </c>
       <c r="U23" s="6" t="n">
-        <v>0.1058708764448293</v>
+        <v>0.1025384604994051</v>
       </c>
       <c r="V23" s="6" t="n">
-        <v>0.06330079521293835</v>
+        <v>0.06489121931864847</v>
       </c>
       <c r="W23" s="6" t="n">
-        <v>0.1626465419628995</v>
+        <v>0.1580768717736664</v>
       </c>
     </row>
     <row r="24">
@@ -6925,67 +6925,67 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>9224</v>
+        <v>10866</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>5218</v>
+        <v>6470</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>14972</v>
+        <v>17086</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.1370676015177119</v>
+        <v>0.1504162790766665</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>0.07754213467813141</v>
+        <v>0.08956435934605392</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>0.2224738402244173</v>
+        <v>0.2365102309820681</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>10890</v>
+        <v>12335</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>6193</v>
+        <v>7369</v>
       </c>
       <c r="M24" s="5" t="n">
-        <v>16529</v>
+        <v>18566</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>0.1496919325685958</v>
+        <v>0.1606264335856247</v>
       </c>
       <c r="O24" s="6" t="n">
-        <v>0.085131994932115</v>
+        <v>0.09595224138774842</v>
       </c>
       <c r="P24" s="6" t="n">
-        <v>0.227204305666118</v>
+        <v>0.2417550269921907</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="R24" s="5" t="n">
-        <v>20114</v>
+        <v>23202</v>
       </c>
       <c r="S24" s="5" t="n">
-        <v>13850</v>
+        <v>15683</v>
       </c>
       <c r="T24" s="5" t="n">
-        <v>28174</v>
+        <v>31193</v>
       </c>
       <c r="U24" s="6" t="n">
-        <v>0.1436255827301719</v>
+        <v>0.1556773261049002</v>
       </c>
       <c r="V24" s="6" t="n">
-        <v>0.09889903234214112</v>
+        <v>0.1052257602787308</v>
       </c>
       <c r="W24" s="6" t="n">
-        <v>0.2011791532289536</v>
+        <v>0.2092983705949708</v>
       </c>
     </row>
     <row r="25">
@@ -6996,67 +6996,67 @@
         </is>
       </c>
       <c r="C25" s="5" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>43319</v>
+        <v>46168</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>35634</v>
+        <v>39008</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>49605</v>
+        <v>52690</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.6437124139011801</v>
+        <v>0.639070225083508</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>0.5295142045382402</v>
+        <v>0.5399620388218344</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>0.7371209344660199</v>
+        <v>0.7293489999904611</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>50983</v>
+        <v>53582</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>44062</v>
+        <v>46397</v>
       </c>
       <c r="M25" s="5" t="n">
-        <v>57207</v>
+        <v>60099</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>0.7007918584572422</v>
+        <v>0.6977328451736421</v>
       </c>
       <c r="O25" s="6" t="n">
-        <v>0.6056580948420994</v>
+        <v>0.6041640056388788</v>
       </c>
       <c r="P25" s="6" t="n">
-        <v>0.7863512098381547</v>
+        <v>0.7825868270392095</v>
       </c>
       <c r="Q25" s="5" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="R25" s="5" t="n">
-        <v>94302</v>
+        <v>99750</v>
       </c>
       <c r="S25" s="5" t="n">
-        <v>83539</v>
+        <v>89915</v>
       </c>
       <c r="T25" s="5" t="n">
-        <v>103305</v>
+        <v>109586</v>
       </c>
       <c r="U25" s="6" t="n">
-        <v>0.6733635632181252</v>
+        <v>0.6692976621730071</v>
       </c>
       <c r="V25" s="6" t="n">
-        <v>0.5965132082453666</v>
+        <v>0.6033081037766561</v>
       </c>
       <c r="W25" s="6" t="n">
-        <v>0.7376481749025615</v>
+        <v>0.7352943100197522</v>
       </c>
     </row>
     <row r="26">
@@ -7073,19 +7073,19 @@
         <v>2630</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>615</v>
+        <v>605</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>6282</v>
+        <v>7300</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.03907785881417459</v>
+        <v>0.0364026662774601</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>0.009132065038866096</v>
+        <v>0.008373999451888976</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>0.09335466270238107</v>
+        <v>0.1010521728389359</v>
       </c>
       <c r="J26" s="5" t="n">
         <v>4</v>
@@ -7094,19 +7094,19 @@
         <v>2655</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>628</v>
+        <v>727</v>
       </c>
       <c r="M26" s="5" t="n">
-        <v>6465</v>
+        <v>6795</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>0.03649725770091456</v>
+        <v>0.034574832652156</v>
       </c>
       <c r="O26" s="6" t="n">
-        <v>0.008626096002201648</v>
+        <v>0.009469550874702064</v>
       </c>
       <c r="P26" s="6" t="n">
-        <v>0.08887109837061523</v>
+        <v>0.08847953255354676</v>
       </c>
       <c r="Q26" s="5" t="n">
         <v>8</v>
@@ -7115,19 +7115,19 @@
         <v>5285</v>
       </c>
       <c r="S26" s="5" t="n">
-        <v>2338</v>
+        <v>2327</v>
       </c>
       <c r="T26" s="5" t="n">
-        <v>10484</v>
+        <v>10322</v>
       </c>
       <c r="U26" s="6" t="n">
-        <v>0.0377373098734505</v>
+        <v>0.03546082757618731</v>
       </c>
       <c r="V26" s="6" t="n">
-        <v>0.01669483269140525</v>
+        <v>0.01561533821809636</v>
       </c>
       <c r="W26" s="6" t="n">
-        <v>0.07485843154016186</v>
+        <v>0.06926035631979317</v>
       </c>
     </row>
     <row r="27">
@@ -7138,16 +7138,16 @@
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>67296</v>
+        <v>72242</v>
       </c>
       <c r="G27" s="6" t="n">
         <v>1</v>
@@ -7159,16 +7159,16 @@
         <v>1</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="M27" s="5" t="n">
-        <v>72750</v>
+        <v>76795</v>
       </c>
       <c r="N27" s="6" t="n">
         <v>1</v>
@@ -7180,16 +7180,16 @@
         <v>1</v>
       </c>
       <c r="Q27" s="5" t="n">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="R27" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="S27" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="T27" s="5" t="n">
-        <v>140046</v>
+        <v>149037</v>
       </c>
       <c r="U27" s="6" t="n">
         <v>1</v>
@@ -7219,19 +7219,19 @@
         <v>20534</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>14690</v>
+        <v>14668</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>28221</v>
+        <v>28648</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.06953390192572956</v>
+        <v>0.06625640786564475</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>0.04974470096925213</v>
+        <v>0.04732664215100515</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>0.09556382909035477</v>
+        <v>0.09243540000168564</v>
       </c>
       <c r="J28" s="5" t="n">
         <v>18</v>
@@ -7240,19 +7240,19 @@
         <v>9822</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>5984</v>
+        <v>5952</v>
       </c>
       <c r="M28" s="5" t="n">
-        <v>16025</v>
+        <v>15677</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>0.04158010159618866</v>
+        <v>0.03950258751054814</v>
       </c>
       <c r="O28" s="6" t="n">
-        <v>0.0253303468865386</v>
+        <v>0.02393648321984446</v>
       </c>
       <c r="P28" s="6" t="n">
-        <v>0.06784006227418887</v>
+        <v>0.06305217076505047</v>
       </c>
       <c r="Q28" s="5" t="n">
         <v>54</v>
@@ -7261,19 +7261,19 @@
         <v>30356</v>
       </c>
       <c r="S28" s="5" t="n">
-        <v>23056</v>
+        <v>21832</v>
       </c>
       <c r="T28" s="5" t="n">
-        <v>39654</v>
+        <v>39931</v>
       </c>
       <c r="U28" s="6" t="n">
-        <v>0.0571109569111312</v>
+        <v>0.05434710160472543</v>
       </c>
       <c r="V28" s="6" t="n">
-        <v>0.04337620179188037</v>
+        <v>0.03908605202554562</v>
       </c>
       <c r="W28" s="6" t="n">
-        <v>0.07460204759140737</v>
+        <v>0.07148771338274433</v>
       </c>
     </row>
     <row r="29">
@@ -7284,67 +7284,67 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>38404</v>
+        <v>38859</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>28527</v>
+        <v>29036</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>50639</v>
+        <v>50262</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.1300435512930515</v>
+        <v>0.1253826275996551</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>0.09659704987445564</v>
+        <v>0.09368918503665173</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>0.1714747123912722</v>
+        <v>0.1621744021396123</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>17816</v>
+        <v>19715</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>11974</v>
+        <v>13362</v>
       </c>
       <c r="M29" s="5" t="n">
-        <v>24843</v>
+        <v>27080</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>0.07542309374672825</v>
+        <v>0.07928893841292615</v>
       </c>
       <c r="O29" s="6" t="n">
-        <v>0.05069207494921473</v>
+        <v>0.05374176233887454</v>
       </c>
       <c r="P29" s="6" t="n">
-        <v>0.1051679823534004</v>
+        <v>0.1089122094984304</v>
       </c>
       <c r="Q29" s="5" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="R29" s="5" t="n">
-        <v>56220</v>
+        <v>58574</v>
       </c>
       <c r="S29" s="5" t="n">
-        <v>45394</v>
+        <v>46661</v>
       </c>
       <c r="T29" s="5" t="n">
-        <v>70464</v>
+        <v>72699</v>
       </c>
       <c r="U29" s="6" t="n">
-        <v>0.1057696803785088</v>
+        <v>0.104864292127024</v>
       </c>
       <c r="V29" s="6" t="n">
-        <v>0.08540154257041084</v>
+        <v>0.08353730110616554</v>
       </c>
       <c r="W29" s="6" t="n">
-        <v>0.1325670641041694</v>
+        <v>0.1301536378381803</v>
       </c>
     </row>
     <row r="30">
@@ -7355,67 +7355,67 @@
         </is>
       </c>
       <c r="C30" s="5" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>62400</v>
+        <v>67890</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>48531</v>
+        <v>55392</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>75793</v>
+        <v>83600</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.2113003858910899</v>
+        <v>0.2190557688248159</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0.164335334888596</v>
+        <v>0.178727015457265</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>0.256651485697376</v>
+        <v>0.2697440014259118</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>38442</v>
+        <v>41944</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>29966</v>
+        <v>33725</v>
       </c>
       <c r="M30" s="5" t="n">
-        <v>48884</v>
+        <v>53835</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>0.1627388332431797</v>
+        <v>0.1686933285679346</v>
       </c>
       <c r="O30" s="6" t="n">
-        <v>0.1268576154895797</v>
+        <v>0.1356363775929846</v>
       </c>
       <c r="P30" s="6" t="n">
-        <v>0.2069432250850004</v>
+        <v>0.2165149259071954</v>
       </c>
       <c r="Q30" s="5" t="n">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="R30" s="5" t="n">
-        <v>100842</v>
+        <v>109835</v>
       </c>
       <c r="S30" s="5" t="n">
-        <v>83743</v>
+        <v>93271</v>
       </c>
       <c r="T30" s="5" t="n">
-        <v>117490</v>
+        <v>128619</v>
       </c>
       <c r="U30" s="6" t="n">
-        <v>0.1897191521677102</v>
+        <v>0.1966372238429889</v>
       </c>
       <c r="V30" s="6" t="n">
-        <v>0.1575502098463926</v>
+        <v>0.1669828629768384</v>
       </c>
       <c r="W30" s="6" t="n">
-        <v>0.2210401311171179</v>
+        <v>0.2302665262046047</v>
       </c>
     </row>
     <row r="31">
@@ -7426,67 +7426,67 @@
         </is>
       </c>
       <c r="C31" s="5" t="n">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>160681</v>
+        <v>169343</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>144308</v>
+        <v>152814</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>176241</v>
+        <v>184409</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.5440988934224992</v>
+        <v>0.5464041087557022</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.4886578117298992</v>
+        <v>0.4930720308199934</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.5967897434437842</v>
+        <v>0.5950156463513958</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>158394</v>
+        <v>165416</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>146846</v>
+        <v>152442</v>
       </c>
       <c r="M31" s="5" t="n">
-        <v>170720</v>
+        <v>176874</v>
       </c>
       <c r="N31" s="6" t="n">
-        <v>0.6705382862218142</v>
+        <v>0.6652796617098348</v>
       </c>
       <c r="O31" s="6" t="n">
-        <v>0.6216523767872832</v>
+        <v>0.613098227416492</v>
       </c>
       <c r="P31" s="6" t="n">
-        <v>0.7227203048937656</v>
+        <v>0.7113613830495057</v>
       </c>
       <c r="Q31" s="5" t="n">
-        <v>456</v>
+        <v>478</v>
       </c>
       <c r="R31" s="5" t="n">
-        <v>319074</v>
+        <v>334760</v>
       </c>
       <c r="S31" s="5" t="n">
-        <v>299339</v>
+        <v>315001</v>
       </c>
       <c r="T31" s="5" t="n">
-        <v>339037</v>
+        <v>355396</v>
       </c>
       <c r="U31" s="6" t="n">
-        <v>0.60028980864361</v>
+        <v>0.5993208641303116</v>
       </c>
       <c r="V31" s="6" t="n">
-        <v>0.563160768622505</v>
+        <v>0.5639471153154629</v>
       </c>
       <c r="W31" s="6" t="n">
-        <v>0.6378464072351873</v>
+        <v>0.6362654989695848</v>
       </c>
     </row>
     <row r="32">
@@ -7503,19 +7503,19 @@
         <v>13296</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>7812</v>
+        <v>8334</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>20024</v>
+        <v>20131</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.04502326746762988</v>
+        <v>0.04290108695418218</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>0.0264528256244437</v>
+        <v>0.02689121781838753</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>0.06780558474788687</v>
+        <v>0.06495411129809432</v>
       </c>
       <c r="J32" s="5" t="n">
         <v>18</v>
@@ -7524,19 +7524,19 @@
         <v>11745</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>6923</v>
+        <v>7109</v>
       </c>
       <c r="M32" s="5" t="n">
-        <v>18359</v>
+        <v>18101</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>0.04971968519208925</v>
+        <v>0.04723548379875631</v>
       </c>
       <c r="O32" s="6" t="n">
-        <v>0.02930601463734402</v>
+        <v>0.02859167592456736</v>
       </c>
       <c r="P32" s="6" t="n">
-        <v>0.07772119987038033</v>
+        <v>0.07279780441381759</v>
       </c>
       <c r="Q32" s="5" t="n">
         <v>38</v>
@@ -7545,19 +7545,19 @@
         <v>25041</v>
       </c>
       <c r="S32" s="5" t="n">
-        <v>17719</v>
+        <v>17996</v>
       </c>
       <c r="T32" s="5" t="n">
-        <v>33945</v>
+        <v>33671</v>
       </c>
       <c r="U32" s="6" t="n">
-        <v>0.04711040189903985</v>
+        <v>0.04483051829495001</v>
       </c>
       <c r="V32" s="6" t="n">
-        <v>0.03333524867077534</v>
+        <v>0.03221805119402989</v>
       </c>
       <c r="W32" s="6" t="n">
-        <v>0.06386237884781724</v>
+        <v>0.06028176938657121</v>
       </c>
     </row>
     <row r="33">
@@ -7568,16 +7568,16 @@
         </is>
       </c>
       <c r="C33" s="5" t="n">
-        <v>409</v>
+        <v>429</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>295315</v>
+        <v>309923</v>
       </c>
       <c r="G33" s="6" t="n">
         <v>1</v>
@@ -7589,16 +7589,16 @@
         <v>1</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>357</v>
+        <v>376</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="M33" s="5" t="n">
-        <v>236219</v>
+        <v>248642</v>
       </c>
       <c r="N33" s="6" t="n">
         <v>1</v>
@@ -7610,16 +7610,16 @@
         <v>1</v>
       </c>
       <c r="Q33" s="5" t="n">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="R33" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="S33" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="T33" s="5" t="n">
-        <v>531534</v>
+        <v>558565</v>
       </c>
       <c r="U33" s="6" t="n">
         <v>1</v>
